--- a/frontend/public/plantillas/Plantilla_Carga_PlanLiga.xlsx
+++ b/frontend/public/plantillas/Plantilla_Carga_PlanLiga.xlsx
@@ -1,49 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12300"/>
   </bookViews>
   <sheets>
-    <sheet name="Datos" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Datos" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Datos!$A$4:$T$5</definedName>
+    <definedName name="_xlnm._FilterDatabase">Datos!$A$4:$T$5</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Plantilla</author>
+    <author>Author</author>
   </authors>
   <commentList>
     <comment ref="A4" authorId="0">
       <text>
         <r>
           <rPr>
+            <charset val="134"/>
             <sz val="10"/>
             <rFont val="SimSun"/>
-            <charset val="134"/>
           </rPr>
-          <t>VARCHAR2(30)
+          <t xml:space="preserve">VARCHAR2(30)
 OBLIGATORIO
 Tipo de plan (ej. PLAN FAMILIAR, PLAN INDIVIDUAL). Max 30 caracteres.</t>
         </r>
@@ -53,11 +40,11 @@
       <text>
         <r>
           <rPr>
+            <charset val="134"/>
             <sz val="10"/>
             <rFont val="SimSun"/>
-            <charset val="134"/>
           </rPr>
-          <t>VARCHAR2(2)
+          <t xml:space="preserve">VARCHAR2(2)
 OBLIGATORIO
 Tipo de documento. Max 2 caracteres (ej. CC, TI, CE, PA).</t>
         </r>
@@ -67,11 +54,11 @@
       <text>
         <r>
           <rPr>
+            <charset val="134"/>
             <sz val="10"/>
             <rFont val="SimSun"/>
-            <charset val="134"/>
           </rPr>
-          <t>VARCHAR2(20)
+          <t xml:space="preserve">VARCHAR2(20)
 OBLIGATORIO
 Numero de documento SIN puntos ni espacios. Se guarda como texto.</t>
         </r>
@@ -81,11 +68,11 @@
       <text>
         <r>
           <rPr>
+            <charset val="134"/>
             <sz val="10"/>
             <rFont val="SimSun"/>
-            <charset val="134"/>
           </rPr>
-          <t>VARCHAR2(20)
+          <t xml:space="preserve">VARCHAR2(20)
 OBLIGATORIO
 Primer nombre. Max 20 caracteres.</t>
         </r>
@@ -95,11 +82,11 @@
       <text>
         <r>
           <rPr>
+            <charset val="134"/>
             <sz val="10"/>
             <rFont val="SimSun"/>
-            <charset val="134"/>
           </rPr>
-          <t>VARCHAR2(20)
+          <t xml:space="preserve">VARCHAR2(20)
 Opcional
 Segundo nombre. Max 20 caracteres.</t>
         </r>
@@ -109,11 +96,11 @@
       <text>
         <r>
           <rPr>
+            <charset val="134"/>
             <sz val="10"/>
             <rFont val="SimSun"/>
-            <charset val="134"/>
           </rPr>
-          <t>VARCHAR2(20)
+          <t xml:space="preserve">VARCHAR2(20)
 OBLIGATORIO
 Primer apellido. Max 20 caracteres.</t>
         </r>
@@ -123,11 +110,11 @@
       <text>
         <r>
           <rPr>
+            <charset val="134"/>
             <sz val="10"/>
             <rFont val="SimSun"/>
-            <charset val="134"/>
           </rPr>
-          <t>VARCHAR2(20)
+          <t xml:space="preserve">VARCHAR2(20)
 Opcional
 Segundo apellido. Max 20 caracteres.</t>
         </r>
@@ -137,11 +124,11 @@
       <text>
         <r>
           <rPr>
+            <charset val="134"/>
             <sz val="10"/>
             <rFont val="SimSun"/>
-            <charset val="134"/>
           </rPr>
-          <t>DATE
+          <t xml:space="preserve">DATE
 OBLIGATORIO
 Fecha de nacimiento. Formato DD/MM/AAAA.</t>
         </r>
@@ -151,11 +138,11 @@
       <text>
         <r>
           <rPr>
+            <charset val="134"/>
             <sz val="10"/>
             <rFont val="SimSun"/>
-            <charset val="134"/>
           </rPr>
-          <t>CHAR(1)
+          <t xml:space="preserve">CHAR(1)
 OBLIGATORIO
 Un solo caracter: M o F.</t>
         </r>
@@ -165,11 +152,11 @@
       <text>
         <r>
           <rPr>
+            <charset val="134"/>
             <sz val="10"/>
             <rFont val="SimSun"/>
-            <charset val="134"/>
           </rPr>
-          <t>VARCHAR2(100)
+          <t xml:space="preserve">VARCHAR2(100)
 Opcional
 Direccion de residencia. Max 100 caracteres.</t>
         </r>
@@ -179,13 +166,15 @@
       <text>
         <r>
           <rPr>
+            <charset val="134"/>
             <sz val="10"/>
             <rFont val="SimSun"/>
-            <charset val="134"/>
           </rPr>
-          <t>VARCHAR2(50)
+          <t xml:space="preserve">VARCHAR2(50)
 OBLIGATORIO
-Municipio. Max 50 caracteres.</t>
+Municipio. Debe coincidir (exacto, o aproximado si tiene un error de tipeo/tilde)
+con el catálogo de municipios de Colombia. Si no se parece a ninguno, esa fila
+queda con error y no se crea.</t>
         </r>
       </text>
     </comment>
@@ -193,13 +182,15 @@
       <text>
         <r>
           <rPr>
+            <charset val="134"/>
             <sz val="10"/>
             <rFont val="SimSun"/>
-            <charset val="134"/>
           </rPr>
-          <t>VARCHAR2(50)
+          <t xml:space="preserve">VARCHAR2(50)
 OBLIGATORIO
-Departamento. Max 50 caracteres.</t>
+Departamento. Debe coincidir (exacto, o aproximado si tiene un error de tipeo/tilde)
+con el catálogo de departamentos de Colombia. Si no se parece a ninguno, esa fila
+queda con error y no se crea.</t>
         </r>
       </text>
     </comment>
@@ -207,11 +198,11 @@
       <text>
         <r>
           <rPr>
+            <charset val="134"/>
             <sz val="10"/>
             <rFont val="SimSun"/>
-            <charset val="134"/>
           </rPr>
-          <t>VARCHAR2(200)
+          <t xml:space="preserve">VARCHAR2(200)
 Opcional
 Correo electronico. Max 200 caracteres.</t>
         </r>
@@ -221,11 +212,11 @@
       <text>
         <r>
           <rPr>
+            <charset val="134"/>
             <sz val="10"/>
             <rFont val="SimSun"/>
-            <charset val="134"/>
           </rPr>
-          <t>VARCHAR2(15)
+          <t xml:space="preserve">VARCHAR2(15)
 Opcional
 Telefono/celular sin espacios. Max 15 caracteres.</t>
         </r>
@@ -235,11 +226,11 @@
       <text>
         <r>
           <rPr>
+            <charset val="134"/>
             <sz val="10"/>
             <rFont val="SimSun"/>
-            <charset val="134"/>
           </rPr>
-          <t>DATE
+          <t xml:space="preserve">DATE
 OBLIGATORIO
 Fecha de inscripcion/ingreso al plan. Formato DD/MM/AAAA.</t>
         </r>
@@ -249,11 +240,11 @@
       <text>
         <r>
           <rPr>
+            <charset val="134"/>
             <sz val="10"/>
             <rFont val="SimSun"/>
-            <charset val="134"/>
           </rPr>
-          <t>VARCHAR2(100)
+          <t xml:space="preserve">VARCHAR2(100)
 Opcional
 Empresa a la que pertenece. Max 100 caracteres.</t>
         </r>
@@ -263,11 +254,11 @@
       <text>
         <r>
           <rPr>
+            <charset val="134"/>
             <sz val="10"/>
             <rFont val="SimSun"/>
-            <charset val="134"/>
           </rPr>
-          <t>VARCHAR2(100)
+          <t xml:space="preserve">VARCHAR2(100)
 OBLIGATORIO
 EPS a la que esta afiliado. Max 100 caracteres.</t>
         </r>
@@ -277,11 +268,11 @@
       <text>
         <r>
           <rPr>
+            <charset val="134"/>
             <sz val="10"/>
             <rFont val="SimSun"/>
-            <charset val="134"/>
           </rPr>
-          <t>VARCHAR2(100)
+          <t xml:space="preserve">VARCHAR2(100)
 Opcional
 Otra EPS, si aplica. Max 100 caracteres.</t>
         </r>
@@ -291,11 +282,11 @@
       <text>
         <r>
           <rPr>
+            <charset val="134"/>
             <sz val="10"/>
             <rFont val="SimSun"/>
-            <charset val="134"/>
           </rPr>
-          <t>VARCHAR2(100)
+          <t xml:space="preserve">VARCHAR2(100)
 Opcional
 Plan de salud complementario (ej. MEDICINA PREPAGADA). NO es el nombre comercial del plan.</t>
         </r>
@@ -305,11 +296,11 @@
       <text>
         <r>
           <rPr>
+            <charset val="134"/>
             <sz val="10"/>
             <rFont val="SimSun"/>
-            <charset val="134"/>
           </rPr>
-          <t>VARCHAR2(100)
+          <t xml:space="preserve">VARCHAR2(100)
 OBLIGATORIO
 Nombre comercial del plan Liga (ej. PLAN LIGA ORO). Max 100 caracteres.</t>
         </r>
@@ -325,7 +316,7 @@
     <t>PLANTILLA DE CARGA MANUAL - INTRANET_PLANLIGA</t>
   </si>
   <si>
-    <t>Diligencie una fila por afiliado a partir de la fila 6. La fila 5 es un EJEMPLO: borrela antes de entregar el archivo. Las columnas con encabezado azul oscuro son OBLIGATORIAS; las de azul claro son opcionales. Pase el cursor sobre cada encabezado para ver la indicacion del campo.
+    <t xml:space="preserve">Diligencie una fila por afiliado a partir de la fila 6. La fila 5 es un EJEMPLO: borrela antes de entregar el archivo. Las columnas con encabezado azul oscuro son OBLIGATORIAS; las de azul claro son opcionales. Pase el cursor sobre cada encabezado para ver la indicacion del campo.
 Campos obligatorios (12): TIPO_PLAN, TIPO, DOCUMENTO, NOMBRE1, APELLIDO1, FECHA_NACIMIENTO, SEXO, CIUDAD, DEPARTAMENTO, FECHA_INGRESO, EPS, PLAN_NOMBRE.</t>
   </si>
   <si>
@@ -443,206 +434,60 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="dd/mm/yyyy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <charset val="134"/>
+      <color rgb="FF1F4E79"/>
       <sz val="14"/>
-      <color rgb="FF1F4E79"/>
       <name val="Arial"/>
+    </font>
+    <font>
       <charset val="134"/>
+      <color theme="1"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <i/>
+      <charset val="134"/>
+      <color rgb="FF595959"/>
       <sz val="10"/>
-      <color rgb="FF595959"/>
       <name val="Arial"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
+      <charset val="134"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="134"/>
     </font>
     <font>
       <i/>
+      <charset val="134"/>
+      <color rgb="FF808080"/>
       <sz val="10"/>
-      <color rgb="FF808080"/>
       <name val="Arial"/>
-      <charset val="134"/>
     </font>
     <font>
+      <charset val="134"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -667,194 +512,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -877,330 +536,44 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Coma" xfId="1" builtinId="3"/>
-    <cellStyle name="Moneda" xfId="2" builtinId="4"/>
-    <cellStyle name="K" xfId="3" builtinId="5"/>
-    <cellStyle name="Coma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Moneda [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hipervínculo" xfId="6" builtinId="8"/>
-    <cellStyle name="Hipervínculo visitado" xfId="7" builtinId="9"/>
-    <cellStyle name="Nota" xfId="8" builtinId="10"/>
-    <cellStyle name="Texto de advertencia" xfId="9" builtinId="11"/>
-    <cellStyle name="Título" xfId="10" builtinId="15"/>
-    <cellStyle name="Texto explicativo" xfId="11" builtinId="53"/>
-    <cellStyle name="Título 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Título 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Título 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Título 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Entrada" xfId="16" builtinId="20"/>
-    <cellStyle name="Salida" xfId="17" builtinId="21"/>
-    <cellStyle name="Cálculo" xfId="18" builtinId="22"/>
-    <cellStyle name="Celda de comprobación" xfId="19" builtinId="23"/>
-    <cellStyle name="Celda vinculada" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Correcto" xfId="22" builtinId="26"/>
-    <cellStyle name="Incorrecto" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutro" xfId="24" builtinId="28"/>
-    <cellStyle name="Énfasis1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Énfasis1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Énfasis1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Énfasis1" xfId="28" builtinId="32"/>
-    <cellStyle name="Énfasis2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Énfasis2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Énfasis2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Énfasis2" xfId="32" builtinId="36"/>
-    <cellStyle name="Énfasis3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Énfasis3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Énfasis3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Énfasis3" xfId="36" builtinId="40"/>
-    <cellStyle name="Énfasis4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Énfasis4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Énfasis4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Énfasis4" xfId="40" builtinId="44"/>
-    <cellStyle name="Énfasis5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Énfasis5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Énfasis5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Énfasis5" xfId="44" builtinId="48"/>
-    <cellStyle name="Énfasis6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Énfasis6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Énfasis6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Énfasis6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1489,10 +862,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T504"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="3" width="12.8571428571429" customWidth="1"/>
@@ -1506,7 +878,7 @@
     <col min="17" max="17" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" spans="1:20">
+    <row r="1" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1522,7 +894,7 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
     </row>
-    <row r="2" ht="82" customHeight="1" spans="1:20">
+    <row r="2" ht="82" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1538,7 +910,7 @@
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
     </row>
-    <row r="3" ht="22" customHeight="1" spans="1:20">
+    <row r="3" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -1552,7 +924,7 @@
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
     </row>
-    <row r="4" ht="30" customHeight="1" spans="1:20">
+    <row r="4" ht="30" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
@@ -1614,7 +986,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>22</v>
       </c>
@@ -1674,7 +1046,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
       <c r="C6" s="11"/>
@@ -1696,7 +1068,7 @@
       <c r="S6" s="10"/>
       <c r="T6" s="10"/>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
@@ -1718,7 +1090,7 @@
       <c r="S7" s="10"/>
       <c r="T7" s="10"/>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="11"/>
@@ -1740,7 +1112,7 @@
       <c r="S8" s="10"/>
       <c r="T8" s="10"/>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="11"/>
@@ -1762,7 +1134,7 @@
       <c r="S9" s="10"/>
       <c r="T9" s="10"/>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
@@ -1784,7 +1156,7 @@
       <c r="S10" s="10"/>
       <c r="T10" s="10"/>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="11"/>
@@ -1806,7 +1178,7 @@
       <c r="S11" s="10"/>
       <c r="T11" s="10"/>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
@@ -1828,7 +1200,7 @@
       <c r="S12" s="10"/>
       <c r="T12" s="10"/>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
@@ -1850,7 +1222,7 @@
       <c r="S13" s="10"/>
       <c r="T13" s="10"/>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
@@ -1872,7 +1244,7 @@
       <c r="S14" s="10"/>
       <c r="T14" s="10"/>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
@@ -1894,7 +1266,7 @@
       <c r="S15" s="10"/>
       <c r="T15" s="10"/>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
@@ -1916,7 +1288,7 @@
       <c r="S16" s="10"/>
       <c r="T16" s="10"/>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
       <c r="B17" s="10"/>
       <c r="C17" s="11"/>
@@ -1938,7 +1310,7 @@
       <c r="S17" s="10"/>
       <c r="T17" s="10"/>
     </row>
-    <row r="18" spans="1:20">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="10"/>
       <c r="B18" s="10"/>
       <c r="C18" s="11"/>
@@ -1960,7 +1332,7 @@
       <c r="S18" s="10"/>
       <c r="T18" s="10"/>
     </row>
-    <row r="19" spans="1:20">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="10"/>
       <c r="B19" s="10"/>
       <c r="C19" s="11"/>
@@ -1982,7 +1354,7 @@
       <c r="S19" s="10"/>
       <c r="T19" s="10"/>
     </row>
-    <row r="20" spans="1:20">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="10"/>
       <c r="B20" s="10"/>
       <c r="C20" s="11"/>
@@ -2004,7 +1376,7 @@
       <c r="S20" s="10"/>
       <c r="T20" s="10"/>
     </row>
-    <row r="21" spans="1:20">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="10"/>
       <c r="C21" s="11"/>
@@ -2026,7 +1398,7 @@
       <c r="S21" s="10"/>
       <c r="T21" s="10"/>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
       <c r="B22" s="10"/>
       <c r="C22" s="11"/>
@@ -2048,7 +1420,7 @@
       <c r="S22" s="10"/>
       <c r="T22" s="10"/>
     </row>
-    <row r="23" spans="1:20">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="10"/>
       <c r="B23" s="10"/>
       <c r="C23" s="11"/>
@@ -2070,7 +1442,7 @@
       <c r="S23" s="10"/>
       <c r="T23" s="10"/>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
@@ -2092,7 +1464,7 @@
       <c r="S24" s="10"/>
       <c r="T24" s="10"/>
     </row>
-    <row r="25" spans="1:20">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
@@ -2114,7 +1486,7 @@
       <c r="S25" s="10"/>
       <c r="T25" s="10"/>
     </row>
-    <row r="26" spans="1:20">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
@@ -2136,7 +1508,7 @@
       <c r="S26" s="10"/>
       <c r="T26" s="10"/>
     </row>
-    <row r="27" spans="1:20">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
@@ -2158,7 +1530,7 @@
       <c r="S27" s="10"/>
       <c r="T27" s="10"/>
     </row>
-    <row r="28" spans="1:20">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
@@ -2180,7 +1552,7 @@
       <c r="S28" s="10"/>
       <c r="T28" s="10"/>
     </row>
-    <row r="29" spans="1:20">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
@@ -2202,7 +1574,7 @@
       <c r="S29" s="10"/>
       <c r="T29" s="10"/>
     </row>
-    <row r="30" spans="1:20">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
       <c r="C30" s="11"/>
@@ -2224,7 +1596,7 @@
       <c r="S30" s="10"/>
       <c r="T30" s="10"/>
     </row>
-    <row r="31" spans="1:20">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="10"/>
       <c r="B31" s="10"/>
       <c r="C31" s="11"/>
@@ -2246,7 +1618,7 @@
       <c r="S31" s="10"/>
       <c r="T31" s="10"/>
     </row>
-    <row r="32" spans="1:20">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="10"/>
       <c r="B32" s="10"/>
       <c r="C32" s="11"/>
@@ -2268,7 +1640,7 @@
       <c r="S32" s="10"/>
       <c r="T32" s="10"/>
     </row>
-    <row r="33" spans="1:20">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="11"/>
@@ -2290,7 +1662,7 @@
       <c r="S33" s="10"/>
       <c r="T33" s="10"/>
     </row>
-    <row r="34" spans="1:20">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="11"/>
@@ -2312,7 +1684,7 @@
       <c r="S34" s="10"/>
       <c r="T34" s="10"/>
     </row>
-    <row r="35" spans="1:20">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
@@ -2334,7 +1706,7 @@
       <c r="S35" s="10"/>
       <c r="T35" s="10"/>
     </row>
-    <row r="36" spans="1:20">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
@@ -2356,7 +1728,7 @@
       <c r="S36" s="10"/>
       <c r="T36" s="10"/>
     </row>
-    <row r="37" spans="1:20">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
@@ -2378,7 +1750,7 @@
       <c r="S37" s="10"/>
       <c r="T37" s="10"/>
     </row>
-    <row r="38" spans="1:20">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
@@ -2400,7 +1772,7 @@
       <c r="S38" s="10"/>
       <c r="T38" s="10"/>
     </row>
-    <row r="39" spans="1:20">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
@@ -2422,7 +1794,7 @@
       <c r="S39" s="10"/>
       <c r="T39" s="10"/>
     </row>
-    <row r="40" spans="1:20">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
@@ -2444,7 +1816,7 @@
       <c r="S40" s="10"/>
       <c r="T40" s="10"/>
     </row>
-    <row r="41" spans="1:20">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
@@ -2466,7 +1838,7 @@
       <c r="S41" s="10"/>
       <c r="T41" s="10"/>
     </row>
-    <row r="42" spans="1:20">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
@@ -2488,7 +1860,7 @@
       <c r="S42" s="10"/>
       <c r="T42" s="10"/>
     </row>
-    <row r="43" spans="1:20">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
@@ -2510,7 +1882,7 @@
       <c r="S43" s="10"/>
       <c r="T43" s="10"/>
     </row>
-    <row r="44" spans="1:20">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
@@ -2532,7 +1904,7 @@
       <c r="S44" s="10"/>
       <c r="T44" s="10"/>
     </row>
-    <row r="45" spans="1:20">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
@@ -2554,7 +1926,7 @@
       <c r="S45" s="10"/>
       <c r="T45" s="10"/>
     </row>
-    <row r="46" spans="1:20">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
@@ -2576,7 +1948,7 @@
       <c r="S46" s="10"/>
       <c r="T46" s="10"/>
     </row>
-    <row r="47" spans="1:20">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
@@ -2598,7 +1970,7 @@
       <c r="S47" s="10"/>
       <c r="T47" s="10"/>
     </row>
-    <row r="48" spans="1:20">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
@@ -2620,7 +1992,7 @@
       <c r="S48" s="10"/>
       <c r="T48" s="10"/>
     </row>
-    <row r="49" spans="1:20">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
@@ -2642,7 +2014,7 @@
       <c r="S49" s="10"/>
       <c r="T49" s="10"/>
     </row>
-    <row r="50" spans="1:20">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
@@ -2664,7 +2036,7 @@
       <c r="S50" s="10"/>
       <c r="T50" s="10"/>
     </row>
-    <row r="51" spans="1:20">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
@@ -2686,7 +2058,7 @@
       <c r="S51" s="10"/>
       <c r="T51" s="10"/>
     </row>
-    <row r="52" spans="1:20">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
@@ -2708,7 +2080,7 @@
       <c r="S52" s="10"/>
       <c r="T52" s="10"/>
     </row>
-    <row r="53" spans="1:20">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
@@ -2730,7 +2102,7 @@
       <c r="S53" s="10"/>
       <c r="T53" s="10"/>
     </row>
-    <row r="54" spans="1:20">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
@@ -2752,7 +2124,7 @@
       <c r="S54" s="10"/>
       <c r="T54" s="10"/>
     </row>
-    <row r="55" spans="1:20">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
@@ -2774,7 +2146,7 @@
       <c r="S55" s="10"/>
       <c r="T55" s="10"/>
     </row>
-    <row r="56" spans="1:20">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
@@ -2796,7 +2168,7 @@
       <c r="S56" s="10"/>
       <c r="T56" s="10"/>
     </row>
-    <row r="57" spans="1:20">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
@@ -2818,7 +2190,7 @@
       <c r="S57" s="10"/>
       <c r="T57" s="10"/>
     </row>
-    <row r="58" spans="1:20">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="10"/>
       <c r="B58" s="10"/>
       <c r="C58" s="11"/>
@@ -2840,7 +2212,7 @@
       <c r="S58" s="10"/>
       <c r="T58" s="10"/>
     </row>
-    <row r="59" spans="1:20">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" s="10"/>
       <c r="B59" s="10"/>
       <c r="C59" s="11"/>
@@ -2862,7 +2234,7 @@
       <c r="S59" s="10"/>
       <c r="T59" s="10"/>
     </row>
-    <row r="60" spans="1:20">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" s="10"/>
       <c r="B60" s="10"/>
       <c r="C60" s="11"/>
@@ -2884,7 +2256,7 @@
       <c r="S60" s="10"/>
       <c r="T60" s="10"/>
     </row>
-    <row r="61" spans="1:20">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" s="10"/>
       <c r="B61" s="10"/>
       <c r="C61" s="11"/>
@@ -2906,7 +2278,7 @@
       <c r="S61" s="10"/>
       <c r="T61" s="10"/>
     </row>
-    <row r="62" spans="1:20">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" s="10"/>
       <c r="B62" s="10"/>
       <c r="C62" s="11"/>
@@ -2928,7 +2300,7 @@
       <c r="S62" s="10"/>
       <c r="T62" s="10"/>
     </row>
-    <row r="63" spans="1:20">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" s="10"/>
       <c r="B63" s="10"/>
       <c r="C63" s="11"/>
@@ -2950,7 +2322,7 @@
       <c r="S63" s="10"/>
       <c r="T63" s="10"/>
     </row>
-    <row r="64" spans="1:20">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="10"/>
       <c r="B64" s="10"/>
       <c r="C64" s="11"/>
@@ -2972,7 +2344,7 @@
       <c r="S64" s="10"/>
       <c r="T64" s="10"/>
     </row>
-    <row r="65" spans="1:20">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" s="10"/>
       <c r="B65" s="10"/>
       <c r="C65" s="11"/>
@@ -2994,7 +2366,7 @@
       <c r="S65" s="10"/>
       <c r="T65" s="10"/>
     </row>
-    <row r="66" spans="1:20">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" s="10"/>
       <c r="B66" s="10"/>
       <c r="C66" s="11"/>
@@ -3016,7 +2388,7 @@
       <c r="S66" s="10"/>
       <c r="T66" s="10"/>
     </row>
-    <row r="67" spans="1:20">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" s="10"/>
       <c r="B67" s="10"/>
       <c r="C67" s="11"/>
@@ -3038,7 +2410,7 @@
       <c r="S67" s="10"/>
       <c r="T67" s="10"/>
     </row>
-    <row r="68" spans="1:20">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" s="10"/>
       <c r="B68" s="10"/>
       <c r="C68" s="11"/>
@@ -3060,7 +2432,7 @@
       <c r="S68" s="10"/>
       <c r="T68" s="10"/>
     </row>
-    <row r="69" spans="1:20">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" s="10"/>
       <c r="B69" s="10"/>
       <c r="C69" s="11"/>
@@ -3082,7 +2454,7 @@
       <c r="S69" s="10"/>
       <c r="T69" s="10"/>
     </row>
-    <row r="70" spans="1:20">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" s="10"/>
       <c r="B70" s="10"/>
       <c r="C70" s="11"/>
@@ -3104,7 +2476,7 @@
       <c r="S70" s="10"/>
       <c r="T70" s="10"/>
     </row>
-    <row r="71" spans="1:20">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" s="10"/>
       <c r="B71" s="10"/>
       <c r="C71" s="11"/>
@@ -3126,7 +2498,7 @@
       <c r="S71" s="10"/>
       <c r="T71" s="10"/>
     </row>
-    <row r="72" spans="1:20">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" s="10"/>
       <c r="B72" s="10"/>
       <c r="C72" s="11"/>
@@ -3148,7 +2520,7 @@
       <c r="S72" s="10"/>
       <c r="T72" s="10"/>
     </row>
-    <row r="73" spans="1:20">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="10"/>
       <c r="B73" s="10"/>
       <c r="C73" s="11"/>
@@ -3170,7 +2542,7 @@
       <c r="S73" s="10"/>
       <c r="T73" s="10"/>
     </row>
-    <row r="74" spans="1:20">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="10"/>
       <c r="B74" s="10"/>
       <c r="C74" s="11"/>
@@ -3192,7 +2564,7 @@
       <c r="S74" s="10"/>
       <c r="T74" s="10"/>
     </row>
-    <row r="75" spans="1:20">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="10"/>
       <c r="B75" s="10"/>
       <c r="C75" s="11"/>
@@ -3214,7 +2586,7 @@
       <c r="S75" s="10"/>
       <c r="T75" s="10"/>
     </row>
-    <row r="76" spans="1:20">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" s="10"/>
       <c r="B76" s="10"/>
       <c r="C76" s="11"/>
@@ -3236,7 +2608,7 @@
       <c r="S76" s="10"/>
       <c r="T76" s="10"/>
     </row>
-    <row r="77" spans="1:20">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="10"/>
       <c r="B77" s="10"/>
       <c r="C77" s="11"/>
@@ -3258,7 +2630,7 @@
       <c r="S77" s="10"/>
       <c r="T77" s="10"/>
     </row>
-    <row r="78" spans="1:20">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" s="10"/>
       <c r="B78" s="10"/>
       <c r="C78" s="11"/>
@@ -3280,7 +2652,7 @@
       <c r="S78" s="10"/>
       <c r="T78" s="10"/>
     </row>
-    <row r="79" spans="1:20">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" s="10"/>
       <c r="B79" s="10"/>
       <c r="C79" s="11"/>
@@ -3302,7 +2674,7 @@
       <c r="S79" s="10"/>
       <c r="T79" s="10"/>
     </row>
-    <row r="80" spans="1:20">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" s="10"/>
       <c r="B80" s="10"/>
       <c r="C80" s="11"/>
@@ -3324,7 +2696,7 @@
       <c r="S80" s="10"/>
       <c r="T80" s="10"/>
     </row>
-    <row r="81" spans="1:20">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" s="10"/>
       <c r="B81" s="10"/>
       <c r="C81" s="11"/>
@@ -3346,7 +2718,7 @@
       <c r="S81" s="10"/>
       <c r="T81" s="10"/>
     </row>
-    <row r="82" spans="1:20">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" s="10"/>
       <c r="B82" s="10"/>
       <c r="C82" s="11"/>
@@ -3368,7 +2740,7 @@
       <c r="S82" s="10"/>
       <c r="T82" s="10"/>
     </row>
-    <row r="83" spans="1:20">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" s="10"/>
       <c r="B83" s="10"/>
       <c r="C83" s="11"/>
@@ -3390,7 +2762,7 @@
       <c r="S83" s="10"/>
       <c r="T83" s="10"/>
     </row>
-    <row r="84" spans="1:20">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" s="10"/>
       <c r="B84" s="10"/>
       <c r="C84" s="11"/>
@@ -3412,7 +2784,7 @@
       <c r="S84" s="10"/>
       <c r="T84" s="10"/>
     </row>
-    <row r="85" spans="1:20">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" s="10"/>
       <c r="B85" s="10"/>
       <c r="C85" s="11"/>
@@ -3434,7 +2806,7 @@
       <c r="S85" s="10"/>
       <c r="T85" s="10"/>
     </row>
-    <row r="86" spans="1:20">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86" s="10"/>
       <c r="B86" s="10"/>
       <c r="C86" s="11"/>
@@ -3456,7 +2828,7 @@
       <c r="S86" s="10"/>
       <c r="T86" s="10"/>
     </row>
-    <row r="87" spans="1:20">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A87" s="10"/>
       <c r="B87" s="10"/>
       <c r="C87" s="11"/>
@@ -3478,7 +2850,7 @@
       <c r="S87" s="10"/>
       <c r="T87" s="10"/>
     </row>
-    <row r="88" spans="1:20">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A88" s="10"/>
       <c r="B88" s="10"/>
       <c r="C88" s="11"/>
@@ -3500,7 +2872,7 @@
       <c r="S88" s="10"/>
       <c r="T88" s="10"/>
     </row>
-    <row r="89" spans="1:20">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89" s="10"/>
       <c r="B89" s="10"/>
       <c r="C89" s="11"/>
@@ -3522,7 +2894,7 @@
       <c r="S89" s="10"/>
       <c r="T89" s="10"/>
     </row>
-    <row r="90" spans="1:20">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90" s="10"/>
       <c r="B90" s="10"/>
       <c r="C90" s="11"/>
@@ -3544,7 +2916,7 @@
       <c r="S90" s="10"/>
       <c r="T90" s="10"/>
     </row>
-    <row r="91" spans="1:20">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" s="10"/>
       <c r="B91" s="10"/>
       <c r="C91" s="11"/>
@@ -3566,7 +2938,7 @@
       <c r="S91" s="10"/>
       <c r="T91" s="10"/>
     </row>
-    <row r="92" spans="1:20">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92" s="10"/>
       <c r="B92" s="10"/>
       <c r="C92" s="11"/>
@@ -3588,7 +2960,7 @@
       <c r="S92" s="10"/>
       <c r="T92" s="10"/>
     </row>
-    <row r="93" spans="1:20">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93" s="10"/>
       <c r="B93" s="10"/>
       <c r="C93" s="11"/>
@@ -3610,7 +2982,7 @@
       <c r="S93" s="10"/>
       <c r="T93" s="10"/>
     </row>
-    <row r="94" spans="1:20">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A94" s="10"/>
       <c r="B94" s="10"/>
       <c r="C94" s="11"/>
@@ -3632,7 +3004,7 @@
       <c r="S94" s="10"/>
       <c r="T94" s="10"/>
     </row>
-    <row r="95" spans="1:20">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95" s="10"/>
       <c r="B95" s="10"/>
       <c r="C95" s="11"/>
@@ -3654,7 +3026,7 @@
       <c r="S95" s="10"/>
       <c r="T95" s="10"/>
     </row>
-    <row r="96" spans="1:20">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A96" s="10"/>
       <c r="B96" s="10"/>
       <c r="C96" s="11"/>
@@ -3676,7 +3048,7 @@
       <c r="S96" s="10"/>
       <c r="T96" s="10"/>
     </row>
-    <row r="97" spans="1:20">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A97" s="10"/>
       <c r="B97" s="10"/>
       <c r="C97" s="11"/>
@@ -3698,7 +3070,7 @@
       <c r="S97" s="10"/>
       <c r="T97" s="10"/>
     </row>
-    <row r="98" spans="1:20">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A98" s="10"/>
       <c r="B98" s="10"/>
       <c r="C98" s="11"/>
@@ -3720,7 +3092,7 @@
       <c r="S98" s="10"/>
       <c r="T98" s="10"/>
     </row>
-    <row r="99" spans="1:20">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A99" s="10"/>
       <c r="B99" s="10"/>
       <c r="C99" s="11"/>
@@ -3742,7 +3114,7 @@
       <c r="S99" s="10"/>
       <c r="T99" s="10"/>
     </row>
-    <row r="100" spans="1:20">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A100" s="10"/>
       <c r="B100" s="10"/>
       <c r="C100" s="11"/>
@@ -3764,7 +3136,7 @@
       <c r="S100" s="10"/>
       <c r="T100" s="10"/>
     </row>
-    <row r="101" spans="1:20">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A101" s="10"/>
       <c r="B101" s="10"/>
       <c r="C101" s="11"/>
@@ -3786,7 +3158,7 @@
       <c r="S101" s="10"/>
       <c r="T101" s="10"/>
     </row>
-    <row r="102" spans="1:20">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A102" s="10"/>
       <c r="B102" s="10"/>
       <c r="C102" s="11"/>
@@ -3808,7 +3180,7 @@
       <c r="S102" s="10"/>
       <c r="T102" s="10"/>
     </row>
-    <row r="103" spans="1:20">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A103" s="10"/>
       <c r="B103" s="10"/>
       <c r="C103" s="11"/>
@@ -3830,7 +3202,7 @@
       <c r="S103" s="10"/>
       <c r="T103" s="10"/>
     </row>
-    <row r="104" spans="1:20">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A104" s="10"/>
       <c r="B104" s="10"/>
       <c r="C104" s="11"/>
@@ -3852,7 +3224,7 @@
       <c r="S104" s="10"/>
       <c r="T104" s="10"/>
     </row>
-    <row r="105" spans="1:20">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A105" s="10"/>
       <c r="B105" s="10"/>
       <c r="C105" s="11"/>
@@ -3874,7 +3246,7 @@
       <c r="S105" s="10"/>
       <c r="T105" s="10"/>
     </row>
-    <row r="106" spans="1:20">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A106" s="10"/>
       <c r="B106" s="10"/>
       <c r="C106" s="11"/>
@@ -3896,7 +3268,7 @@
       <c r="S106" s="10"/>
       <c r="T106" s="10"/>
     </row>
-    <row r="107" spans="1:20">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A107" s="10"/>
       <c r="B107" s="10"/>
       <c r="C107" s="11"/>
@@ -3918,7 +3290,7 @@
       <c r="S107" s="10"/>
       <c r="T107" s="10"/>
     </row>
-    <row r="108" spans="1:20">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A108" s="10"/>
       <c r="B108" s="10"/>
       <c r="C108" s="11"/>
@@ -3940,7 +3312,7 @@
       <c r="S108" s="10"/>
       <c r="T108" s="10"/>
     </row>
-    <row r="109" spans="1:20">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A109" s="10"/>
       <c r="B109" s="10"/>
       <c r="C109" s="11"/>
@@ -3962,7 +3334,7 @@
       <c r="S109" s="10"/>
       <c r="T109" s="10"/>
     </row>
-    <row r="110" spans="1:20">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A110" s="10"/>
       <c r="B110" s="10"/>
       <c r="C110" s="11"/>
@@ -3984,7 +3356,7 @@
       <c r="S110" s="10"/>
       <c r="T110" s="10"/>
     </row>
-    <row r="111" spans="1:20">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A111" s="10"/>
       <c r="B111" s="10"/>
       <c r="C111" s="11"/>
@@ -4006,7 +3378,7 @@
       <c r="S111" s="10"/>
       <c r="T111" s="10"/>
     </row>
-    <row r="112" spans="1:20">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A112" s="10"/>
       <c r="B112" s="10"/>
       <c r="C112" s="11"/>
@@ -4028,7 +3400,7 @@
       <c r="S112" s="10"/>
       <c r="T112" s="10"/>
     </row>
-    <row r="113" spans="1:20">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A113" s="10"/>
       <c r="B113" s="10"/>
       <c r="C113" s="11"/>
@@ -4050,7 +3422,7 @@
       <c r="S113" s="10"/>
       <c r="T113" s="10"/>
     </row>
-    <row r="114" spans="1:20">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A114" s="10"/>
       <c r="B114" s="10"/>
       <c r="C114" s="11"/>
@@ -4072,7 +3444,7 @@
       <c r="S114" s="10"/>
       <c r="T114" s="10"/>
     </row>
-    <row r="115" spans="1:20">
+    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A115" s="10"/>
       <c r="B115" s="10"/>
       <c r="C115" s="11"/>
@@ -4094,7 +3466,7 @@
       <c r="S115" s="10"/>
       <c r="T115" s="10"/>
     </row>
-    <row r="116" spans="1:20">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A116" s="10"/>
       <c r="B116" s="10"/>
       <c r="C116" s="11"/>
@@ -4116,7 +3488,7 @@
       <c r="S116" s="10"/>
       <c r="T116" s="10"/>
     </row>
-    <row r="117" spans="1:20">
+    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A117" s="10"/>
       <c r="B117" s="10"/>
       <c r="C117" s="11"/>
@@ -4138,7 +3510,7 @@
       <c r="S117" s="10"/>
       <c r="T117" s="10"/>
     </row>
-    <row r="118" spans="1:20">
+    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A118" s="10"/>
       <c r="B118" s="10"/>
       <c r="C118" s="11"/>
@@ -4160,7 +3532,7 @@
       <c r="S118" s="10"/>
       <c r="T118" s="10"/>
     </row>
-    <row r="119" spans="1:20">
+    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A119" s="10"/>
       <c r="B119" s="10"/>
       <c r="C119" s="11"/>
@@ -4182,7 +3554,7 @@
       <c r="S119" s="10"/>
       <c r="T119" s="10"/>
     </row>
-    <row r="120" spans="1:20">
+    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A120" s="10"/>
       <c r="B120" s="10"/>
       <c r="C120" s="11"/>
@@ -4204,7 +3576,7 @@
       <c r="S120" s="10"/>
       <c r="T120" s="10"/>
     </row>
-    <row r="121" spans="1:20">
+    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A121" s="10"/>
       <c r="B121" s="10"/>
       <c r="C121" s="11"/>
@@ -4226,7 +3598,7 @@
       <c r="S121" s="10"/>
       <c r="T121" s="10"/>
     </row>
-    <row r="122" spans="1:20">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A122" s="10"/>
       <c r="B122" s="10"/>
       <c r="C122" s="11"/>
@@ -4248,7 +3620,7 @@
       <c r="S122" s="10"/>
       <c r="T122" s="10"/>
     </row>
-    <row r="123" spans="1:20">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A123" s="10"/>
       <c r="B123" s="10"/>
       <c r="C123" s="11"/>
@@ -4270,7 +3642,7 @@
       <c r="S123" s="10"/>
       <c r="T123" s="10"/>
     </row>
-    <row r="124" spans="1:20">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A124" s="10"/>
       <c r="B124" s="10"/>
       <c r="C124" s="11"/>
@@ -4292,7 +3664,7 @@
       <c r="S124" s="10"/>
       <c r="T124" s="10"/>
     </row>
-    <row r="125" spans="1:20">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A125" s="10"/>
       <c r="B125" s="10"/>
       <c r="C125" s="11"/>
@@ -4314,7 +3686,7 @@
       <c r="S125" s="10"/>
       <c r="T125" s="10"/>
     </row>
-    <row r="126" spans="1:20">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A126" s="10"/>
       <c r="B126" s="10"/>
       <c r="C126" s="11"/>
@@ -4336,7 +3708,7 @@
       <c r="S126" s="10"/>
       <c r="T126" s="10"/>
     </row>
-    <row r="127" spans="1:20">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A127" s="10"/>
       <c r="B127" s="10"/>
       <c r="C127" s="11"/>
@@ -4358,7 +3730,7 @@
       <c r="S127" s="10"/>
       <c r="T127" s="10"/>
     </row>
-    <row r="128" spans="1:20">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A128" s="10"/>
       <c r="B128" s="10"/>
       <c r="C128" s="11"/>
@@ -4380,7 +3752,7 @@
       <c r="S128" s="10"/>
       <c r="T128" s="10"/>
     </row>
-    <row r="129" spans="1:20">
+    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A129" s="10"/>
       <c r="B129" s="10"/>
       <c r="C129" s="11"/>
@@ -4402,7 +3774,7 @@
       <c r="S129" s="10"/>
       <c r="T129" s="10"/>
     </row>
-    <row r="130" spans="1:20">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A130" s="10"/>
       <c r="B130" s="10"/>
       <c r="C130" s="11"/>
@@ -4424,7 +3796,7 @@
       <c r="S130" s="10"/>
       <c r="T130" s="10"/>
     </row>
-    <row r="131" spans="1:20">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A131" s="10"/>
       <c r="B131" s="10"/>
       <c r="C131" s="11"/>
@@ -4446,7 +3818,7 @@
       <c r="S131" s="10"/>
       <c r="T131" s="10"/>
     </row>
-    <row r="132" spans="1:20">
+    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A132" s="10"/>
       <c r="B132" s="10"/>
       <c r="C132" s="11"/>
@@ -4468,7 +3840,7 @@
       <c r="S132" s="10"/>
       <c r="T132" s="10"/>
     </row>
-    <row r="133" spans="1:20">
+    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A133" s="10"/>
       <c r="B133" s="10"/>
       <c r="C133" s="11"/>
@@ -4490,7 +3862,7 @@
       <c r="S133" s="10"/>
       <c r="T133" s="10"/>
     </row>
-    <row r="134" spans="1:20">
+    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A134" s="10"/>
       <c r="B134" s="10"/>
       <c r="C134" s="11"/>
@@ -4512,7 +3884,7 @@
       <c r="S134" s="10"/>
       <c r="T134" s="10"/>
     </row>
-    <row r="135" spans="1:20">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A135" s="10"/>
       <c r="B135" s="10"/>
       <c r="C135" s="11"/>
@@ -4534,7 +3906,7 @@
       <c r="S135" s="10"/>
       <c r="T135" s="10"/>
     </row>
-    <row r="136" spans="1:20">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A136" s="10"/>
       <c r="B136" s="10"/>
       <c r="C136" s="11"/>
@@ -4556,7 +3928,7 @@
       <c r="S136" s="10"/>
       <c r="T136" s="10"/>
     </row>
-    <row r="137" spans="1:20">
+    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A137" s="10"/>
       <c r="B137" s="10"/>
       <c r="C137" s="11"/>
@@ -4578,7 +3950,7 @@
       <c r="S137" s="10"/>
       <c r="T137" s="10"/>
     </row>
-    <row r="138" spans="1:20">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A138" s="10"/>
       <c r="B138" s="10"/>
       <c r="C138" s="11"/>
@@ -4600,7 +3972,7 @@
       <c r="S138" s="10"/>
       <c r="T138" s="10"/>
     </row>
-    <row r="139" spans="1:20">
+    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A139" s="10"/>
       <c r="B139" s="10"/>
       <c r="C139" s="11"/>
@@ -4622,7 +3994,7 @@
       <c r="S139" s="10"/>
       <c r="T139" s="10"/>
     </row>
-    <row r="140" spans="1:20">
+    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A140" s="10"/>
       <c r="B140" s="10"/>
       <c r="C140" s="11"/>
@@ -4644,7 +4016,7 @@
       <c r="S140" s="10"/>
       <c r="T140" s="10"/>
     </row>
-    <row r="141" spans="1:20">
+    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A141" s="10"/>
       <c r="B141" s="10"/>
       <c r="C141" s="11"/>
@@ -4666,7 +4038,7 @@
       <c r="S141" s="10"/>
       <c r="T141" s="10"/>
     </row>
-    <row r="142" spans="1:20">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A142" s="10"/>
       <c r="B142" s="10"/>
       <c r="C142" s="11"/>
@@ -4688,7 +4060,7 @@
       <c r="S142" s="10"/>
       <c r="T142" s="10"/>
     </row>
-    <row r="143" spans="1:20">
+    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A143" s="10"/>
       <c r="B143" s="10"/>
       <c r="C143" s="11"/>
@@ -4710,7 +4082,7 @@
       <c r="S143" s="10"/>
       <c r="T143" s="10"/>
     </row>
-    <row r="144" spans="1:20">
+    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A144" s="10"/>
       <c r="B144" s="10"/>
       <c r="C144" s="11"/>
@@ -4732,7 +4104,7 @@
       <c r="S144" s="10"/>
       <c r="T144" s="10"/>
     </row>
-    <row r="145" spans="1:20">
+    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A145" s="10"/>
       <c r="B145" s="10"/>
       <c r="C145" s="11"/>
@@ -4754,7 +4126,7 @@
       <c r="S145" s="10"/>
       <c r="T145" s="10"/>
     </row>
-    <row r="146" spans="1:20">
+    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A146" s="10"/>
       <c r="B146" s="10"/>
       <c r="C146" s="11"/>
@@ -4776,7 +4148,7 @@
       <c r="S146" s="10"/>
       <c r="T146" s="10"/>
     </row>
-    <row r="147" spans="1:20">
+    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A147" s="10"/>
       <c r="B147" s="10"/>
       <c r="C147" s="11"/>
@@ -4798,7 +4170,7 @@
       <c r="S147" s="10"/>
       <c r="T147" s="10"/>
     </row>
-    <row r="148" spans="1:20">
+    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A148" s="10"/>
       <c r="B148" s="10"/>
       <c r="C148" s="11"/>
@@ -4820,7 +4192,7 @@
       <c r="S148" s="10"/>
       <c r="T148" s="10"/>
     </row>
-    <row r="149" spans="1:20">
+    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A149" s="10"/>
       <c r="B149" s="10"/>
       <c r="C149" s="11"/>
@@ -4842,7 +4214,7 @@
       <c r="S149" s="10"/>
       <c r="T149" s="10"/>
     </row>
-    <row r="150" spans="1:20">
+    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A150" s="10"/>
       <c r="B150" s="10"/>
       <c r="C150" s="11"/>
@@ -4864,7 +4236,7 @@
       <c r="S150" s="10"/>
       <c r="T150" s="10"/>
     </row>
-    <row r="151" spans="1:20">
+    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A151" s="10"/>
       <c r="B151" s="10"/>
       <c r="C151" s="11"/>
@@ -4886,7 +4258,7 @@
       <c r="S151" s="10"/>
       <c r="T151" s="10"/>
     </row>
-    <row r="152" spans="1:20">
+    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A152" s="10"/>
       <c r="B152" s="10"/>
       <c r="C152" s="11"/>
@@ -4908,7 +4280,7 @@
       <c r="S152" s="10"/>
       <c r="T152" s="10"/>
     </row>
-    <row r="153" spans="1:20">
+    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A153" s="10"/>
       <c r="B153" s="10"/>
       <c r="C153" s="11"/>
@@ -4930,7 +4302,7 @@
       <c r="S153" s="10"/>
       <c r="T153" s="10"/>
     </row>
-    <row r="154" spans="1:20">
+    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A154" s="10"/>
       <c r="B154" s="10"/>
       <c r="C154" s="11"/>
@@ -4952,7 +4324,7 @@
       <c r="S154" s="10"/>
       <c r="T154" s="10"/>
     </row>
-    <row r="155" spans="1:20">
+    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A155" s="10"/>
       <c r="B155" s="10"/>
       <c r="C155" s="11"/>
@@ -4974,7 +4346,7 @@
       <c r="S155" s="10"/>
       <c r="T155" s="10"/>
     </row>
-    <row r="156" spans="1:20">
+    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A156" s="10"/>
       <c r="B156" s="10"/>
       <c r="C156" s="11"/>
@@ -4996,7 +4368,7 @@
       <c r="S156" s="10"/>
       <c r="T156" s="10"/>
     </row>
-    <row r="157" spans="1:20">
+    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A157" s="10"/>
       <c r="B157" s="10"/>
       <c r="C157" s="11"/>
@@ -5018,7 +4390,7 @@
       <c r="S157" s="10"/>
       <c r="T157" s="10"/>
     </row>
-    <row r="158" spans="1:20">
+    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A158" s="10"/>
       <c r="B158" s="10"/>
       <c r="C158" s="11"/>
@@ -5040,7 +4412,7 @@
       <c r="S158" s="10"/>
       <c r="T158" s="10"/>
     </row>
-    <row r="159" spans="1:20">
+    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A159" s="10"/>
       <c r="B159" s="10"/>
       <c r="C159" s="11"/>
@@ -5062,7 +4434,7 @@
       <c r="S159" s="10"/>
       <c r="T159" s="10"/>
     </row>
-    <row r="160" spans="1:20">
+    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A160" s="10"/>
       <c r="B160" s="10"/>
       <c r="C160" s="11"/>
@@ -5084,7 +4456,7 @@
       <c r="S160" s="10"/>
       <c r="T160" s="10"/>
     </row>
-    <row r="161" spans="1:20">
+    <row r="161" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A161" s="10"/>
       <c r="B161" s="10"/>
       <c r="C161" s="11"/>
@@ -5106,7 +4478,7 @@
       <c r="S161" s="10"/>
       <c r="T161" s="10"/>
     </row>
-    <row r="162" spans="1:20">
+    <row r="162" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A162" s="10"/>
       <c r="B162" s="10"/>
       <c r="C162" s="11"/>
@@ -5128,7 +4500,7 @@
       <c r="S162" s="10"/>
       <c r="T162" s="10"/>
     </row>
-    <row r="163" spans="1:20">
+    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A163" s="10"/>
       <c r="B163" s="10"/>
       <c r="C163" s="11"/>
@@ -5150,7 +4522,7 @@
       <c r="S163" s="10"/>
       <c r="T163" s="10"/>
     </row>
-    <row r="164" spans="1:20">
+    <row r="164" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A164" s="10"/>
       <c r="B164" s="10"/>
       <c r="C164" s="11"/>
@@ -5172,7 +4544,7 @@
       <c r="S164" s="10"/>
       <c r="T164" s="10"/>
     </row>
-    <row r="165" spans="1:20">
+    <row r="165" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A165" s="10"/>
       <c r="B165" s="10"/>
       <c r="C165" s="11"/>
@@ -5194,7 +4566,7 @@
       <c r="S165" s="10"/>
       <c r="T165" s="10"/>
     </row>
-    <row r="166" spans="1:20">
+    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A166" s="10"/>
       <c r="B166" s="10"/>
       <c r="C166" s="11"/>
@@ -5216,7 +4588,7 @@
       <c r="S166" s="10"/>
       <c r="T166" s="10"/>
     </row>
-    <row r="167" spans="1:20">
+    <row r="167" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A167" s="10"/>
       <c r="B167" s="10"/>
       <c r="C167" s="11"/>
@@ -5238,7 +4610,7 @@
       <c r="S167" s="10"/>
       <c r="T167" s="10"/>
     </row>
-    <row r="168" spans="1:20">
+    <row r="168" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A168" s="10"/>
       <c r="B168" s="10"/>
       <c r="C168" s="11"/>
@@ -5260,7 +4632,7 @@
       <c r="S168" s="10"/>
       <c r="T168" s="10"/>
     </row>
-    <row r="169" spans="1:20">
+    <row r="169" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A169" s="10"/>
       <c r="B169" s="10"/>
       <c r="C169" s="11"/>
@@ -5282,7 +4654,7 @@
       <c r="S169" s="10"/>
       <c r="T169" s="10"/>
     </row>
-    <row r="170" spans="1:20">
+    <row r="170" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A170" s="10"/>
       <c r="B170" s="10"/>
       <c r="C170" s="11"/>
@@ -5304,7 +4676,7 @@
       <c r="S170" s="10"/>
       <c r="T170" s="10"/>
     </row>
-    <row r="171" spans="1:20">
+    <row r="171" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A171" s="10"/>
       <c r="B171" s="10"/>
       <c r="C171" s="11"/>
@@ -5326,7 +4698,7 @@
       <c r="S171" s="10"/>
       <c r="T171" s="10"/>
     </row>
-    <row r="172" spans="1:20">
+    <row r="172" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A172" s="10"/>
       <c r="B172" s="10"/>
       <c r="C172" s="11"/>
@@ -5348,7 +4720,7 @@
       <c r="S172" s="10"/>
       <c r="T172" s="10"/>
     </row>
-    <row r="173" spans="1:20">
+    <row r="173" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A173" s="10"/>
       <c r="B173" s="10"/>
       <c r="C173" s="11"/>
@@ -5370,7 +4742,7 @@
       <c r="S173" s="10"/>
       <c r="T173" s="10"/>
     </row>
-    <row r="174" spans="1:20">
+    <row r="174" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A174" s="10"/>
       <c r="B174" s="10"/>
       <c r="C174" s="11"/>
@@ -5392,7 +4764,7 @@
       <c r="S174" s="10"/>
       <c r="T174" s="10"/>
     </row>
-    <row r="175" spans="1:20">
+    <row r="175" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A175" s="10"/>
       <c r="B175" s="10"/>
       <c r="C175" s="11"/>
@@ -5414,7 +4786,7 @@
       <c r="S175" s="10"/>
       <c r="T175" s="10"/>
     </row>
-    <row r="176" spans="1:20">
+    <row r="176" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A176" s="10"/>
       <c r="B176" s="10"/>
       <c r="C176" s="11"/>
@@ -5436,7 +4808,7 @@
       <c r="S176" s="10"/>
       <c r="T176" s="10"/>
     </row>
-    <row r="177" spans="1:20">
+    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A177" s="10"/>
       <c r="B177" s="10"/>
       <c r="C177" s="11"/>
@@ -5458,7 +4830,7 @@
       <c r="S177" s="10"/>
       <c r="T177" s="10"/>
     </row>
-    <row r="178" spans="1:20">
+    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A178" s="10"/>
       <c r="B178" s="10"/>
       <c r="C178" s="11"/>
@@ -5480,7 +4852,7 @@
       <c r="S178" s="10"/>
       <c r="T178" s="10"/>
     </row>
-    <row r="179" spans="1:20">
+    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A179" s="10"/>
       <c r="B179" s="10"/>
       <c r="C179" s="11"/>
@@ -5502,7 +4874,7 @@
       <c r="S179" s="10"/>
       <c r="T179" s="10"/>
     </row>
-    <row r="180" spans="1:20">
+    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A180" s="10"/>
       <c r="B180" s="10"/>
       <c r="C180" s="11"/>
@@ -5524,7 +4896,7 @@
       <c r="S180" s="10"/>
       <c r="T180" s="10"/>
     </row>
-    <row r="181" spans="1:20">
+    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A181" s="10"/>
       <c r="B181" s="10"/>
       <c r="C181" s="11"/>
@@ -5546,7 +4918,7 @@
       <c r="S181" s="10"/>
       <c r="T181" s="10"/>
     </row>
-    <row r="182" spans="1:20">
+    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A182" s="10"/>
       <c r="B182" s="10"/>
       <c r="C182" s="11"/>
@@ -5568,7 +4940,7 @@
       <c r="S182" s="10"/>
       <c r="T182" s="10"/>
     </row>
-    <row r="183" spans="1:20">
+    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A183" s="10"/>
       <c r="B183" s="10"/>
       <c r="C183" s="11"/>
@@ -5590,7 +4962,7 @@
       <c r="S183" s="10"/>
       <c r="T183" s="10"/>
     </row>
-    <row r="184" spans="1:20">
+    <row r="184" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A184" s="10"/>
       <c r="B184" s="10"/>
       <c r="C184" s="11"/>
@@ -5612,7 +4984,7 @@
       <c r="S184" s="10"/>
       <c r="T184" s="10"/>
     </row>
-    <row r="185" spans="1:20">
+    <row r="185" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A185" s="10"/>
       <c r="B185" s="10"/>
       <c r="C185" s="11"/>
@@ -5634,7 +5006,7 @@
       <c r="S185" s="10"/>
       <c r="T185" s="10"/>
     </row>
-    <row r="186" spans="1:20">
+    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A186" s="10"/>
       <c r="B186" s="10"/>
       <c r="C186" s="11"/>
@@ -5656,7 +5028,7 @@
       <c r="S186" s="10"/>
       <c r="T186" s="10"/>
     </row>
-    <row r="187" spans="1:20">
+    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A187" s="10"/>
       <c r="B187" s="10"/>
       <c r="C187" s="11"/>
@@ -5678,7 +5050,7 @@
       <c r="S187" s="10"/>
       <c r="T187" s="10"/>
     </row>
-    <row r="188" spans="1:20">
+    <row r="188" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A188" s="10"/>
       <c r="B188" s="10"/>
       <c r="C188" s="11"/>
@@ -5700,7 +5072,7 @@
       <c r="S188" s="10"/>
       <c r="T188" s="10"/>
     </row>
-    <row r="189" spans="1:20">
+    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A189" s="10"/>
       <c r="B189" s="10"/>
       <c r="C189" s="11"/>
@@ -5722,7 +5094,7 @@
       <c r="S189" s="10"/>
       <c r="T189" s="10"/>
     </row>
-    <row r="190" spans="1:20">
+    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A190" s="10"/>
       <c r="B190" s="10"/>
       <c r="C190" s="11"/>
@@ -5744,7 +5116,7 @@
       <c r="S190" s="10"/>
       <c r="T190" s="10"/>
     </row>
-    <row r="191" spans="1:20">
+    <row r="191" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A191" s="10"/>
       <c r="B191" s="10"/>
       <c r="C191" s="11"/>
@@ -5766,7 +5138,7 @@
       <c r="S191" s="10"/>
       <c r="T191" s="10"/>
     </row>
-    <row r="192" spans="1:20">
+    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A192" s="10"/>
       <c r="B192" s="10"/>
       <c r="C192" s="11"/>
@@ -5788,7 +5160,7 @@
       <c r="S192" s="10"/>
       <c r="T192" s="10"/>
     </row>
-    <row r="193" spans="1:20">
+    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A193" s="10"/>
       <c r="B193" s="10"/>
       <c r="C193" s="11"/>
@@ -5810,7 +5182,7 @@
       <c r="S193" s="10"/>
       <c r="T193" s="10"/>
     </row>
-    <row r="194" spans="1:20">
+    <row r="194" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A194" s="10"/>
       <c r="B194" s="10"/>
       <c r="C194" s="11"/>
@@ -5832,7 +5204,7 @@
       <c r="S194" s="10"/>
       <c r="T194" s="10"/>
     </row>
-    <row r="195" spans="1:20">
+    <row r="195" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A195" s="10"/>
       <c r="B195" s="10"/>
       <c r="C195" s="11"/>
@@ -5854,7 +5226,7 @@
       <c r="S195" s="10"/>
       <c r="T195" s="10"/>
     </row>
-    <row r="196" spans="1:20">
+    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A196" s="10"/>
       <c r="B196" s="10"/>
       <c r="C196" s="11"/>
@@ -5876,7 +5248,7 @@
       <c r="S196" s="10"/>
       <c r="T196" s="10"/>
     </row>
-    <row r="197" spans="1:20">
+    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A197" s="10"/>
       <c r="B197" s="10"/>
       <c r="C197" s="11"/>
@@ -5898,7 +5270,7 @@
       <c r="S197" s="10"/>
       <c r="T197" s="10"/>
     </row>
-    <row r="198" spans="1:20">
+    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A198" s="10"/>
       <c r="B198" s="10"/>
       <c r="C198" s="11"/>
@@ -5920,7 +5292,7 @@
       <c r="S198" s="10"/>
       <c r="T198" s="10"/>
     </row>
-    <row r="199" spans="1:20">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A199" s="10"/>
       <c r="B199" s="10"/>
       <c r="C199" s="11"/>
@@ -5942,7 +5314,7 @@
       <c r="S199" s="10"/>
       <c r="T199" s="10"/>
     </row>
-    <row r="200" spans="1:20">
+    <row r="200" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A200" s="10"/>
       <c r="B200" s="10"/>
       <c r="C200" s="11"/>
@@ -5964,7 +5336,7 @@
       <c r="S200" s="10"/>
       <c r="T200" s="10"/>
     </row>
-    <row r="201" spans="1:20">
+    <row r="201" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A201" s="10"/>
       <c r="B201" s="10"/>
       <c r="C201" s="11"/>
@@ -5986,7 +5358,7 @@
       <c r="S201" s="10"/>
       <c r="T201" s="10"/>
     </row>
-    <row r="202" spans="1:20">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A202" s="10"/>
       <c r="B202" s="10"/>
       <c r="C202" s="11"/>
@@ -6008,7 +5380,7 @@
       <c r="S202" s="10"/>
       <c r="T202" s="10"/>
     </row>
-    <row r="203" spans="1:20">
+    <row r="203" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A203" s="10"/>
       <c r="B203" s="10"/>
       <c r="C203" s="11"/>
@@ -6030,7 +5402,7 @@
       <c r="S203" s="10"/>
       <c r="T203" s="10"/>
     </row>
-    <row r="204" spans="1:20">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A204" s="10"/>
       <c r="B204" s="10"/>
       <c r="C204" s="11"/>
@@ -6052,7 +5424,7 @@
       <c r="S204" s="10"/>
       <c r="T204" s="10"/>
     </row>
-    <row r="205" spans="1:20">
+    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A205" s="10"/>
       <c r="B205" s="10"/>
       <c r="C205" s="11"/>
@@ -6074,7 +5446,7 @@
       <c r="S205" s="10"/>
       <c r="T205" s="10"/>
     </row>
-    <row r="206" spans="1:20">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A206" s="10"/>
       <c r="B206" s="10"/>
       <c r="C206" s="11"/>
@@ -6096,7 +5468,7 @@
       <c r="S206" s="10"/>
       <c r="T206" s="10"/>
     </row>
-    <row r="207" spans="1:20">
+    <row r="207" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A207" s="10"/>
       <c r="B207" s="10"/>
       <c r="C207" s="11"/>
@@ -6118,7 +5490,7 @@
       <c r="S207" s="10"/>
       <c r="T207" s="10"/>
     </row>
-    <row r="208" spans="1:20">
+    <row r="208" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A208" s="10"/>
       <c r="B208" s="10"/>
       <c r="C208" s="11"/>
@@ -6140,7 +5512,7 @@
       <c r="S208" s="10"/>
       <c r="T208" s="10"/>
     </row>
-    <row r="209" spans="1:20">
+    <row r="209" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A209" s="10"/>
       <c r="B209" s="10"/>
       <c r="C209" s="11"/>
@@ -6162,7 +5534,7 @@
       <c r="S209" s="10"/>
       <c r="T209" s="10"/>
     </row>
-    <row r="210" spans="1:20">
+    <row r="210" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A210" s="10"/>
       <c r="B210" s="10"/>
       <c r="C210" s="11"/>
@@ -6184,7 +5556,7 @@
       <c r="S210" s="10"/>
       <c r="T210" s="10"/>
     </row>
-    <row r="211" spans="1:20">
+    <row r="211" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A211" s="10"/>
       <c r="B211" s="10"/>
       <c r="C211" s="11"/>
@@ -6206,7 +5578,7 @@
       <c r="S211" s="10"/>
       <c r="T211" s="10"/>
     </row>
-    <row r="212" spans="1:20">
+    <row r="212" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A212" s="10"/>
       <c r="B212" s="10"/>
       <c r="C212" s="11"/>
@@ -6228,7 +5600,7 @@
       <c r="S212" s="10"/>
       <c r="T212" s="10"/>
     </row>
-    <row r="213" spans="1:20">
+    <row r="213" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A213" s="10"/>
       <c r="B213" s="10"/>
       <c r="C213" s="11"/>
@@ -6250,7 +5622,7 @@
       <c r="S213" s="10"/>
       <c r="T213" s="10"/>
     </row>
-    <row r="214" spans="1:20">
+    <row r="214" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A214" s="10"/>
       <c r="B214" s="10"/>
       <c r="C214" s="11"/>
@@ -6272,7 +5644,7 @@
       <c r="S214" s="10"/>
       <c r="T214" s="10"/>
     </row>
-    <row r="215" spans="1:20">
+    <row r="215" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A215" s="10"/>
       <c r="B215" s="10"/>
       <c r="C215" s="11"/>
@@ -6294,7 +5666,7 @@
       <c r="S215" s="10"/>
       <c r="T215" s="10"/>
     </row>
-    <row r="216" spans="1:20">
+    <row r="216" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A216" s="10"/>
       <c r="B216" s="10"/>
       <c r="C216" s="11"/>
@@ -6316,7 +5688,7 @@
       <c r="S216" s="10"/>
       <c r="T216" s="10"/>
     </row>
-    <row r="217" spans="1:20">
+    <row r="217" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A217" s="10"/>
       <c r="B217" s="10"/>
       <c r="C217" s="11"/>
@@ -6338,7 +5710,7 @@
       <c r="S217" s="10"/>
       <c r="T217" s="10"/>
     </row>
-    <row r="218" spans="1:20">
+    <row r="218" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A218" s="10"/>
       <c r="B218" s="10"/>
       <c r="C218" s="11"/>
@@ -6360,7 +5732,7 @@
       <c r="S218" s="10"/>
       <c r="T218" s="10"/>
     </row>
-    <row r="219" spans="1:20">
+    <row r="219" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A219" s="10"/>
       <c r="B219" s="10"/>
       <c r="C219" s="11"/>
@@ -6382,7 +5754,7 @@
       <c r="S219" s="10"/>
       <c r="T219" s="10"/>
     </row>
-    <row r="220" spans="1:20">
+    <row r="220" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A220" s="10"/>
       <c r="B220" s="10"/>
       <c r="C220" s="11"/>
@@ -6404,7 +5776,7 @@
       <c r="S220" s="10"/>
       <c r="T220" s="10"/>
     </row>
-    <row r="221" spans="1:20">
+    <row r="221" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A221" s="10"/>
       <c r="B221" s="10"/>
       <c r="C221" s="11"/>
@@ -6426,7 +5798,7 @@
       <c r="S221" s="10"/>
       <c r="T221" s="10"/>
     </row>
-    <row r="222" spans="1:20">
+    <row r="222" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A222" s="10"/>
       <c r="B222" s="10"/>
       <c r="C222" s="11"/>
@@ -6448,7 +5820,7 @@
       <c r="S222" s="10"/>
       <c r="T222" s="10"/>
     </row>
-    <row r="223" spans="1:20">
+    <row r="223" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A223" s="10"/>
       <c r="B223" s="10"/>
       <c r="C223" s="11"/>
@@ -6470,7 +5842,7 @@
       <c r="S223" s="10"/>
       <c r="T223" s="10"/>
     </row>
-    <row r="224" spans="1:20">
+    <row r="224" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A224" s="10"/>
       <c r="B224" s="10"/>
       <c r="C224" s="11"/>
@@ -6492,7 +5864,7 @@
       <c r="S224" s="10"/>
       <c r="T224" s="10"/>
     </row>
-    <row r="225" spans="1:20">
+    <row r="225" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A225" s="10"/>
       <c r="B225" s="10"/>
       <c r="C225" s="11"/>
@@ -6514,7 +5886,7 @@
       <c r="S225" s="10"/>
       <c r="T225" s="10"/>
     </row>
-    <row r="226" spans="1:20">
+    <row r="226" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A226" s="10"/>
       <c r="B226" s="10"/>
       <c r="C226" s="11"/>
@@ -6536,7 +5908,7 @@
       <c r="S226" s="10"/>
       <c r="T226" s="10"/>
     </row>
-    <row r="227" spans="1:20">
+    <row r="227" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A227" s="10"/>
       <c r="B227" s="10"/>
       <c r="C227" s="11"/>
@@ -6558,7 +5930,7 @@
       <c r="S227" s="10"/>
       <c r="T227" s="10"/>
     </row>
-    <row r="228" spans="1:20">
+    <row r="228" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A228" s="10"/>
       <c r="B228" s="10"/>
       <c r="C228" s="11"/>
@@ -6580,7 +5952,7 @@
       <c r="S228" s="10"/>
       <c r="T228" s="10"/>
     </row>
-    <row r="229" spans="1:20">
+    <row r="229" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A229" s="10"/>
       <c r="B229" s="10"/>
       <c r="C229" s="11"/>
@@ -6602,7 +5974,7 @@
       <c r="S229" s="10"/>
       <c r="T229" s="10"/>
     </row>
-    <row r="230" spans="1:20">
+    <row r="230" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A230" s="10"/>
       <c r="B230" s="10"/>
       <c r="C230" s="11"/>
@@ -6624,7 +5996,7 @@
       <c r="S230" s="10"/>
       <c r="T230" s="10"/>
     </row>
-    <row r="231" spans="1:20">
+    <row r="231" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A231" s="10"/>
       <c r="B231" s="10"/>
       <c r="C231" s="11"/>
@@ -6646,7 +6018,7 @@
       <c r="S231" s="10"/>
       <c r="T231" s="10"/>
     </row>
-    <row r="232" spans="1:20">
+    <row r="232" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A232" s="10"/>
       <c r="B232" s="10"/>
       <c r="C232" s="11"/>
@@ -6668,7 +6040,7 @@
       <c r="S232" s="10"/>
       <c r="T232" s="10"/>
     </row>
-    <row r="233" spans="1:20">
+    <row r="233" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A233" s="10"/>
       <c r="B233" s="10"/>
       <c r="C233" s="11"/>
@@ -6690,7 +6062,7 @@
       <c r="S233" s="10"/>
       <c r="T233" s="10"/>
     </row>
-    <row r="234" spans="1:20">
+    <row r="234" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A234" s="10"/>
       <c r="B234" s="10"/>
       <c r="C234" s="11"/>
@@ -6712,7 +6084,7 @@
       <c r="S234" s="10"/>
       <c r="T234" s="10"/>
     </row>
-    <row r="235" spans="1:20">
+    <row r="235" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A235" s="10"/>
       <c r="B235" s="10"/>
       <c r="C235" s="11"/>
@@ -6734,7 +6106,7 @@
       <c r="S235" s="10"/>
       <c r="T235" s="10"/>
     </row>
-    <row r="236" spans="1:20">
+    <row r="236" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A236" s="10"/>
       <c r="B236" s="10"/>
       <c r="C236" s="11"/>
@@ -6756,7 +6128,7 @@
       <c r="S236" s="10"/>
       <c r="T236" s="10"/>
     </row>
-    <row r="237" spans="1:20">
+    <row r="237" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A237" s="10"/>
       <c r="B237" s="10"/>
       <c r="C237" s="11"/>
@@ -6778,7 +6150,7 @@
       <c r="S237" s="10"/>
       <c r="T237" s="10"/>
     </row>
-    <row r="238" spans="1:20">
+    <row r="238" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A238" s="10"/>
       <c r="B238" s="10"/>
       <c r="C238" s="11"/>
@@ -6800,7 +6172,7 @@
       <c r="S238" s="10"/>
       <c r="T238" s="10"/>
     </row>
-    <row r="239" spans="1:20">
+    <row r="239" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A239" s="10"/>
       <c r="B239" s="10"/>
       <c r="C239" s="11"/>
@@ -6822,7 +6194,7 @@
       <c r="S239" s="10"/>
       <c r="T239" s="10"/>
     </row>
-    <row r="240" spans="1:20">
+    <row r="240" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A240" s="10"/>
       <c r="B240" s="10"/>
       <c r="C240" s="11"/>
@@ -6844,7 +6216,7 @@
       <c r="S240" s="10"/>
       <c r="T240" s="10"/>
     </row>
-    <row r="241" spans="1:20">
+    <row r="241" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A241" s="10"/>
       <c r="B241" s="10"/>
       <c r="C241" s="11"/>
@@ -6866,7 +6238,7 @@
       <c r="S241" s="10"/>
       <c r="T241" s="10"/>
     </row>
-    <row r="242" spans="1:20">
+    <row r="242" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A242" s="10"/>
       <c r="B242" s="10"/>
       <c r="C242" s="11"/>
@@ -6888,7 +6260,7 @@
       <c r="S242" s="10"/>
       <c r="T242" s="10"/>
     </row>
-    <row r="243" spans="1:20">
+    <row r="243" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A243" s="10"/>
       <c r="B243" s="10"/>
       <c r="C243" s="11"/>
@@ -6910,7 +6282,7 @@
       <c r="S243" s="10"/>
       <c r="T243" s="10"/>
     </row>
-    <row r="244" spans="1:20">
+    <row r="244" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A244" s="10"/>
       <c r="B244" s="10"/>
       <c r="C244" s="11"/>
@@ -6932,7 +6304,7 @@
       <c r="S244" s="10"/>
       <c r="T244" s="10"/>
     </row>
-    <row r="245" spans="1:20">
+    <row r="245" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A245" s="10"/>
       <c r="B245" s="10"/>
       <c r="C245" s="11"/>
@@ -6954,7 +6326,7 @@
       <c r="S245" s="10"/>
       <c r="T245" s="10"/>
     </row>
-    <row r="246" spans="1:20">
+    <row r="246" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A246" s="10"/>
       <c r="B246" s="10"/>
       <c r="C246" s="11"/>
@@ -6976,7 +6348,7 @@
       <c r="S246" s="10"/>
       <c r="T246" s="10"/>
     </row>
-    <row r="247" spans="1:20">
+    <row r="247" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A247" s="10"/>
       <c r="B247" s="10"/>
       <c r="C247" s="11"/>
@@ -6998,7 +6370,7 @@
       <c r="S247" s="10"/>
       <c r="T247" s="10"/>
     </row>
-    <row r="248" spans="1:20">
+    <row r="248" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A248" s="10"/>
       <c r="B248" s="10"/>
       <c r="C248" s="11"/>
@@ -7020,7 +6392,7 @@
       <c r="S248" s="10"/>
       <c r="T248" s="10"/>
     </row>
-    <row r="249" spans="1:20">
+    <row r="249" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A249" s="10"/>
       <c r="B249" s="10"/>
       <c r="C249" s="11"/>
@@ -7042,7 +6414,7 @@
       <c r="S249" s="10"/>
       <c r="T249" s="10"/>
     </row>
-    <row r="250" spans="1:20">
+    <row r="250" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A250" s="10"/>
       <c r="B250" s="10"/>
       <c r="C250" s="11"/>
@@ -7064,7 +6436,7 @@
       <c r="S250" s="10"/>
       <c r="T250" s="10"/>
     </row>
-    <row r="251" spans="1:20">
+    <row r="251" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A251" s="10"/>
       <c r="B251" s="10"/>
       <c r="C251" s="11"/>
@@ -7086,7 +6458,7 @@
       <c r="S251" s="10"/>
       <c r="T251" s="10"/>
     </row>
-    <row r="252" spans="1:20">
+    <row r="252" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A252" s="10"/>
       <c r="B252" s="10"/>
       <c r="C252" s="11"/>
@@ -7108,7 +6480,7 @@
       <c r="S252" s="10"/>
       <c r="T252" s="10"/>
     </row>
-    <row r="253" spans="1:20">
+    <row r="253" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A253" s="10"/>
       <c r="B253" s="10"/>
       <c r="C253" s="11"/>
@@ -7130,7 +6502,7 @@
       <c r="S253" s="10"/>
       <c r="T253" s="10"/>
     </row>
-    <row r="254" spans="1:20">
+    <row r="254" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A254" s="10"/>
       <c r="B254" s="10"/>
       <c r="C254" s="11"/>
@@ -7152,7 +6524,7 @@
       <c r="S254" s="10"/>
       <c r="T254" s="10"/>
     </row>
-    <row r="255" spans="1:20">
+    <row r="255" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A255" s="10"/>
       <c r="B255" s="10"/>
       <c r="C255" s="11"/>
@@ -7174,7 +6546,7 @@
       <c r="S255" s="10"/>
       <c r="T255" s="10"/>
     </row>
-    <row r="256" spans="1:20">
+    <row r="256" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A256" s="10"/>
       <c r="B256" s="10"/>
       <c r="C256" s="11"/>
@@ -7196,7 +6568,7 @@
       <c r="S256" s="10"/>
       <c r="T256" s="10"/>
     </row>
-    <row r="257" spans="1:20">
+    <row r="257" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A257" s="10"/>
       <c r="B257" s="10"/>
       <c r="C257" s="11"/>
@@ -7218,7 +6590,7 @@
       <c r="S257" s="10"/>
       <c r="T257" s="10"/>
     </row>
-    <row r="258" spans="1:20">
+    <row r="258" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A258" s="10"/>
       <c r="B258" s="10"/>
       <c r="C258" s="11"/>
@@ -7240,7 +6612,7 @@
       <c r="S258" s="10"/>
       <c r="T258" s="10"/>
     </row>
-    <row r="259" spans="1:20">
+    <row r="259" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A259" s="10"/>
       <c r="B259" s="10"/>
       <c r="C259" s="11"/>
@@ -7262,7 +6634,7 @@
       <c r="S259" s="10"/>
       <c r="T259" s="10"/>
     </row>
-    <row r="260" spans="1:20">
+    <row r="260" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A260" s="10"/>
       <c r="B260" s="10"/>
       <c r="C260" s="11"/>
@@ -7284,7 +6656,7 @@
       <c r="S260" s="10"/>
       <c r="T260" s="10"/>
     </row>
-    <row r="261" spans="1:20">
+    <row r="261" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A261" s="10"/>
       <c r="B261" s="10"/>
       <c r="C261" s="11"/>
@@ -7306,7 +6678,7 @@
       <c r="S261" s="10"/>
       <c r="T261" s="10"/>
     </row>
-    <row r="262" spans="1:20">
+    <row r="262" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A262" s="10"/>
       <c r="B262" s="10"/>
       <c r="C262" s="11"/>
@@ -7328,7 +6700,7 @@
       <c r="S262" s="10"/>
       <c r="T262" s="10"/>
     </row>
-    <row r="263" spans="1:20">
+    <row r="263" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A263" s="10"/>
       <c r="B263" s="10"/>
       <c r="C263" s="11"/>
@@ -7350,7 +6722,7 @@
       <c r="S263" s="10"/>
       <c r="T263" s="10"/>
     </row>
-    <row r="264" spans="1:20">
+    <row r="264" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A264" s="10"/>
       <c r="B264" s="10"/>
       <c r="C264" s="11"/>
@@ -7372,7 +6744,7 @@
       <c r="S264" s="10"/>
       <c r="T264" s="10"/>
     </row>
-    <row r="265" spans="1:20">
+    <row r="265" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A265" s="10"/>
       <c r="B265" s="10"/>
       <c r="C265" s="11"/>
@@ -7394,7 +6766,7 @@
       <c r="S265" s="10"/>
       <c r="T265" s="10"/>
     </row>
-    <row r="266" spans="1:20">
+    <row r="266" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A266" s="10"/>
       <c r="B266" s="10"/>
       <c r="C266" s="11"/>
@@ -7416,7 +6788,7 @@
       <c r="S266" s="10"/>
       <c r="T266" s="10"/>
     </row>
-    <row r="267" spans="1:20">
+    <row r="267" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A267" s="10"/>
       <c r="B267" s="10"/>
       <c r="C267" s="11"/>
@@ -7438,7 +6810,7 @@
       <c r="S267" s="10"/>
       <c r="T267" s="10"/>
     </row>
-    <row r="268" spans="1:20">
+    <row r="268" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A268" s="10"/>
       <c r="B268" s="10"/>
       <c r="C268" s="11"/>
@@ -7460,7 +6832,7 @@
       <c r="S268" s="10"/>
       <c r="T268" s="10"/>
     </row>
-    <row r="269" spans="1:20">
+    <row r="269" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A269" s="10"/>
       <c r="B269" s="10"/>
       <c r="C269" s="11"/>
@@ -7482,7 +6854,7 @@
       <c r="S269" s="10"/>
       <c r="T269" s="10"/>
     </row>
-    <row r="270" spans="1:20">
+    <row r="270" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A270" s="10"/>
       <c r="B270" s="10"/>
       <c r="C270" s="11"/>
@@ -7504,7 +6876,7 @@
       <c r="S270" s="10"/>
       <c r="T270" s="10"/>
     </row>
-    <row r="271" spans="1:20">
+    <row r="271" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A271" s="10"/>
       <c r="B271" s="10"/>
       <c r="C271" s="11"/>
@@ -7526,7 +6898,7 @@
       <c r="S271" s="10"/>
       <c r="T271" s="10"/>
     </row>
-    <row r="272" spans="1:20">
+    <row r="272" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A272" s="10"/>
       <c r="B272" s="10"/>
       <c r="C272" s="11"/>
@@ -7548,7 +6920,7 @@
       <c r="S272" s="10"/>
       <c r="T272" s="10"/>
     </row>
-    <row r="273" spans="1:20">
+    <row r="273" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A273" s="10"/>
       <c r="B273" s="10"/>
       <c r="C273" s="11"/>
@@ -7570,7 +6942,7 @@
       <c r="S273" s="10"/>
       <c r="T273" s="10"/>
     </row>
-    <row r="274" spans="1:20">
+    <row r="274" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A274" s="10"/>
       <c r="B274" s="10"/>
       <c r="C274" s="11"/>
@@ -7592,7 +6964,7 @@
       <c r="S274" s="10"/>
       <c r="T274" s="10"/>
     </row>
-    <row r="275" spans="1:20">
+    <row r="275" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A275" s="10"/>
       <c r="B275" s="10"/>
       <c r="C275" s="11"/>
@@ -7614,7 +6986,7 @@
       <c r="S275" s="10"/>
       <c r="T275" s="10"/>
     </row>
-    <row r="276" spans="1:20">
+    <row r="276" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A276" s="10"/>
       <c r="B276" s="10"/>
       <c r="C276" s="11"/>
@@ -7636,7 +7008,7 @@
       <c r="S276" s="10"/>
       <c r="T276" s="10"/>
     </row>
-    <row r="277" spans="1:20">
+    <row r="277" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A277" s="10"/>
       <c r="B277" s="10"/>
       <c r="C277" s="11"/>
@@ -7658,7 +7030,7 @@
       <c r="S277" s="10"/>
       <c r="T277" s="10"/>
     </row>
-    <row r="278" spans="1:20">
+    <row r="278" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A278" s="10"/>
       <c r="B278" s="10"/>
       <c r="C278" s="11"/>
@@ -7680,7 +7052,7 @@
       <c r="S278" s="10"/>
       <c r="T278" s="10"/>
     </row>
-    <row r="279" spans="1:20">
+    <row r="279" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A279" s="10"/>
       <c r="B279" s="10"/>
       <c r="C279" s="11"/>
@@ -7702,7 +7074,7 @@
       <c r="S279" s="10"/>
       <c r="T279" s="10"/>
     </row>
-    <row r="280" spans="1:20">
+    <row r="280" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A280" s="10"/>
       <c r="B280" s="10"/>
       <c r="C280" s="11"/>
@@ -7724,7 +7096,7 @@
       <c r="S280" s="10"/>
       <c r="T280" s="10"/>
     </row>
-    <row r="281" spans="1:20">
+    <row r="281" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A281" s="10"/>
       <c r="B281" s="10"/>
       <c r="C281" s="11"/>
@@ -7746,7 +7118,7 @@
       <c r="S281" s="10"/>
       <c r="T281" s="10"/>
     </row>
-    <row r="282" spans="1:20">
+    <row r="282" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A282" s="10"/>
       <c r="B282" s="10"/>
       <c r="C282" s="11"/>
@@ -7768,7 +7140,7 @@
       <c r="S282" s="10"/>
       <c r="T282" s="10"/>
     </row>
-    <row r="283" spans="1:20">
+    <row r="283" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A283" s="10"/>
       <c r="B283" s="10"/>
       <c r="C283" s="11"/>
@@ -7790,7 +7162,7 @@
       <c r="S283" s="10"/>
       <c r="T283" s="10"/>
     </row>
-    <row r="284" spans="1:20">
+    <row r="284" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A284" s="10"/>
       <c r="B284" s="10"/>
       <c r="C284" s="11"/>
@@ -7812,7 +7184,7 @@
       <c r="S284" s="10"/>
       <c r="T284" s="10"/>
     </row>
-    <row r="285" spans="1:20">
+    <row r="285" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A285" s="10"/>
       <c r="B285" s="10"/>
       <c r="C285" s="11"/>
@@ -7834,7 +7206,7 @@
       <c r="S285" s="10"/>
       <c r="T285" s="10"/>
     </row>
-    <row r="286" spans="1:20">
+    <row r="286" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A286" s="10"/>
       <c r="B286" s="10"/>
       <c r="C286" s="11"/>
@@ -7856,7 +7228,7 @@
       <c r="S286" s="10"/>
       <c r="T286" s="10"/>
     </row>
-    <row r="287" spans="1:20">
+    <row r="287" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A287" s="10"/>
       <c r="B287" s="10"/>
       <c r="C287" s="11"/>
@@ -7878,7 +7250,7 @@
       <c r="S287" s="10"/>
       <c r="T287" s="10"/>
     </row>
-    <row r="288" spans="1:20">
+    <row r="288" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A288" s="10"/>
       <c r="B288" s="10"/>
       <c r="C288" s="11"/>
@@ -7900,7 +7272,7 @@
       <c r="S288" s="10"/>
       <c r="T288" s="10"/>
     </row>
-    <row r="289" spans="1:20">
+    <row r="289" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A289" s="10"/>
       <c r="B289" s="10"/>
       <c r="C289" s="11"/>
@@ -7922,7 +7294,7 @@
       <c r="S289" s="10"/>
       <c r="T289" s="10"/>
     </row>
-    <row r="290" spans="1:20">
+    <row r="290" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A290" s="10"/>
       <c r="B290" s="10"/>
       <c r="C290" s="11"/>
@@ -7944,7 +7316,7 @@
       <c r="S290" s="10"/>
       <c r="T290" s="10"/>
     </row>
-    <row r="291" spans="1:20">
+    <row r="291" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A291" s="10"/>
       <c r="B291" s="10"/>
       <c r="C291" s="11"/>
@@ -7966,7 +7338,7 @@
       <c r="S291" s="10"/>
       <c r="T291" s="10"/>
     </row>
-    <row r="292" spans="1:20">
+    <row r="292" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A292" s="10"/>
       <c r="B292" s="10"/>
       <c r="C292" s="11"/>
@@ -7988,7 +7360,7 @@
       <c r="S292" s="10"/>
       <c r="T292" s="10"/>
     </row>
-    <row r="293" spans="1:20">
+    <row r="293" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A293" s="10"/>
       <c r="B293" s="10"/>
       <c r="C293" s="11"/>
@@ -8010,7 +7382,7 @@
       <c r="S293" s="10"/>
       <c r="T293" s="10"/>
     </row>
-    <row r="294" spans="1:20">
+    <row r="294" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A294" s="10"/>
       <c r="B294" s="10"/>
       <c r="C294" s="11"/>
@@ -8032,7 +7404,7 @@
       <c r="S294" s="10"/>
       <c r="T294" s="10"/>
     </row>
-    <row r="295" spans="1:20">
+    <row r="295" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A295" s="10"/>
       <c r="B295" s="10"/>
       <c r="C295" s="11"/>
@@ -8054,7 +7426,7 @@
       <c r="S295" s="10"/>
       <c r="T295" s="10"/>
     </row>
-    <row r="296" spans="1:20">
+    <row r="296" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A296" s="10"/>
       <c r="B296" s="10"/>
       <c r="C296" s="11"/>
@@ -8076,7 +7448,7 @@
       <c r="S296" s="10"/>
       <c r="T296" s="10"/>
     </row>
-    <row r="297" spans="1:20">
+    <row r="297" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A297" s="10"/>
       <c r="B297" s="10"/>
       <c r="C297" s="11"/>
@@ -8098,7 +7470,7 @@
       <c r="S297" s="10"/>
       <c r="T297" s="10"/>
     </row>
-    <row r="298" spans="1:20">
+    <row r="298" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A298" s="10"/>
       <c r="B298" s="10"/>
       <c r="C298" s="11"/>
@@ -8120,7 +7492,7 @@
       <c r="S298" s="10"/>
       <c r="T298" s="10"/>
     </row>
-    <row r="299" spans="1:20">
+    <row r="299" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A299" s="10"/>
       <c r="B299" s="10"/>
       <c r="C299" s="11"/>
@@ -8142,7 +7514,7 @@
       <c r="S299" s="10"/>
       <c r="T299" s="10"/>
     </row>
-    <row r="300" spans="1:20">
+    <row r="300" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A300" s="10"/>
       <c r="B300" s="10"/>
       <c r="C300" s="11"/>
@@ -8164,7 +7536,7 @@
       <c r="S300" s="10"/>
       <c r="T300" s="10"/>
     </row>
-    <row r="301" spans="1:20">
+    <row r="301" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A301" s="10"/>
       <c r="B301" s="10"/>
       <c r="C301" s="11"/>
@@ -8186,7 +7558,7 @@
       <c r="S301" s="10"/>
       <c r="T301" s="10"/>
     </row>
-    <row r="302" spans="1:20">
+    <row r="302" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A302" s="10"/>
       <c r="B302" s="10"/>
       <c r="C302" s="11"/>
@@ -8208,7 +7580,7 @@
       <c r="S302" s="10"/>
       <c r="T302" s="10"/>
     </row>
-    <row r="303" spans="1:20">
+    <row r="303" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A303" s="10"/>
       <c r="B303" s="10"/>
       <c r="C303" s="11"/>
@@ -8230,7 +7602,7 @@
       <c r="S303" s="10"/>
       <c r="T303" s="10"/>
     </row>
-    <row r="304" spans="1:20">
+    <row r="304" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A304" s="10"/>
       <c r="B304" s="10"/>
       <c r="C304" s="11"/>
@@ -8252,7 +7624,7 @@
       <c r="S304" s="10"/>
       <c r="T304" s="10"/>
     </row>
-    <row r="305" spans="1:20">
+    <row r="305" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A305" s="10"/>
       <c r="B305" s="10"/>
       <c r="C305" s="11"/>
@@ -8274,7 +7646,7 @@
       <c r="S305" s="10"/>
       <c r="T305" s="10"/>
     </row>
-    <row r="306" spans="1:20">
+    <row r="306" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A306" s="10"/>
       <c r="B306" s="10"/>
       <c r="C306" s="11"/>
@@ -8296,7 +7668,7 @@
       <c r="S306" s="10"/>
       <c r="T306" s="10"/>
     </row>
-    <row r="307" spans="1:20">
+    <row r="307" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A307" s="10"/>
       <c r="B307" s="10"/>
       <c r="C307" s="11"/>
@@ -8318,7 +7690,7 @@
       <c r="S307" s="10"/>
       <c r="T307" s="10"/>
     </row>
-    <row r="308" spans="1:20">
+    <row r="308" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A308" s="10"/>
       <c r="B308" s="10"/>
       <c r="C308" s="11"/>
@@ -8340,7 +7712,7 @@
       <c r="S308" s="10"/>
       <c r="T308" s="10"/>
     </row>
-    <row r="309" spans="1:20">
+    <row r="309" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A309" s="10"/>
       <c r="B309" s="10"/>
       <c r="C309" s="11"/>
@@ -8362,7 +7734,7 @@
       <c r="S309" s="10"/>
       <c r="T309" s="10"/>
     </row>
-    <row r="310" spans="1:20">
+    <row r="310" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A310" s="10"/>
       <c r="B310" s="10"/>
       <c r="C310" s="11"/>
@@ -8384,7 +7756,7 @@
       <c r="S310" s="10"/>
       <c r="T310" s="10"/>
     </row>
-    <row r="311" spans="1:20">
+    <row r="311" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A311" s="10"/>
       <c r="B311" s="10"/>
       <c r="C311" s="11"/>
@@ -8406,7 +7778,7 @@
       <c r="S311" s="10"/>
       <c r="T311" s="10"/>
     </row>
-    <row r="312" spans="1:20">
+    <row r="312" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A312" s="10"/>
       <c r="B312" s="10"/>
       <c r="C312" s="11"/>
@@ -8428,7 +7800,7 @@
       <c r="S312" s="10"/>
       <c r="T312" s="10"/>
     </row>
-    <row r="313" spans="1:20">
+    <row r="313" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A313" s="10"/>
       <c r="B313" s="10"/>
       <c r="C313" s="11"/>
@@ -8450,7 +7822,7 @@
       <c r="S313" s="10"/>
       <c r="T313" s="10"/>
     </row>
-    <row r="314" spans="1:20">
+    <row r="314" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A314" s="10"/>
       <c r="B314" s="10"/>
       <c r="C314" s="11"/>
@@ -8472,7 +7844,7 @@
       <c r="S314" s="10"/>
       <c r="T314" s="10"/>
     </row>
-    <row r="315" spans="1:20">
+    <row r="315" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A315" s="10"/>
       <c r="B315" s="10"/>
       <c r="C315" s="11"/>
@@ -8494,7 +7866,7 @@
       <c r="S315" s="10"/>
       <c r="T315" s="10"/>
     </row>
-    <row r="316" spans="1:20">
+    <row r="316" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A316" s="10"/>
       <c r="B316" s="10"/>
       <c r="C316" s="11"/>
@@ -8516,7 +7888,7 @@
       <c r="S316" s="10"/>
       <c r="T316" s="10"/>
     </row>
-    <row r="317" spans="1:20">
+    <row r="317" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A317" s="10"/>
       <c r="B317" s="10"/>
       <c r="C317" s="11"/>
@@ -8538,7 +7910,7 @@
       <c r="S317" s="10"/>
       <c r="T317" s="10"/>
     </row>
-    <row r="318" spans="1:20">
+    <row r="318" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A318" s="10"/>
       <c r="B318" s="10"/>
       <c r="C318" s="11"/>
@@ -8560,7 +7932,7 @@
       <c r="S318" s="10"/>
       <c r="T318" s="10"/>
     </row>
-    <row r="319" spans="1:20">
+    <row r="319" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A319" s="10"/>
       <c r="B319" s="10"/>
       <c r="C319" s="11"/>
@@ -8582,7 +7954,7 @@
       <c r="S319" s="10"/>
       <c r="T319" s="10"/>
     </row>
-    <row r="320" spans="1:20">
+    <row r="320" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A320" s="10"/>
       <c r="B320" s="10"/>
       <c r="C320" s="11"/>
@@ -8604,7 +7976,7 @@
       <c r="S320" s="10"/>
       <c r="T320" s="10"/>
     </row>
-    <row r="321" spans="1:20">
+    <row r="321" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A321" s="10"/>
       <c r="B321" s="10"/>
       <c r="C321" s="11"/>
@@ -8626,7 +7998,7 @@
       <c r="S321" s="10"/>
       <c r="T321" s="10"/>
     </row>
-    <row r="322" spans="1:20">
+    <row r="322" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A322" s="10"/>
       <c r="B322" s="10"/>
       <c r="C322" s="11"/>
@@ -8648,7 +8020,7 @@
       <c r="S322" s="10"/>
       <c r="T322" s="10"/>
     </row>
-    <row r="323" spans="1:20">
+    <row r="323" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A323" s="10"/>
       <c r="B323" s="10"/>
       <c r="C323" s="11"/>
@@ -8670,7 +8042,7 @@
       <c r="S323" s="10"/>
       <c r="T323" s="10"/>
     </row>
-    <row r="324" spans="1:20">
+    <row r="324" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A324" s="10"/>
       <c r="B324" s="10"/>
       <c r="C324" s="11"/>
@@ -8692,7 +8064,7 @@
       <c r="S324" s="10"/>
       <c r="T324" s="10"/>
     </row>
-    <row r="325" spans="1:20">
+    <row r="325" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A325" s="10"/>
       <c r="B325" s="10"/>
       <c r="C325" s="11"/>
@@ -8714,7 +8086,7 @@
       <c r="S325" s="10"/>
       <c r="T325" s="10"/>
     </row>
-    <row r="326" spans="1:20">
+    <row r="326" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A326" s="10"/>
       <c r="B326" s="10"/>
       <c r="C326" s="11"/>
@@ -8736,7 +8108,7 @@
       <c r="S326" s="10"/>
       <c r="T326" s="10"/>
     </row>
-    <row r="327" spans="1:20">
+    <row r="327" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A327" s="10"/>
       <c r="B327" s="10"/>
       <c r="C327" s="11"/>
@@ -8758,7 +8130,7 @@
       <c r="S327" s="10"/>
       <c r="T327" s="10"/>
     </row>
-    <row r="328" spans="1:20">
+    <row r="328" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A328" s="10"/>
       <c r="B328" s="10"/>
       <c r="C328" s="11"/>
@@ -8780,7 +8152,7 @@
       <c r="S328" s="10"/>
       <c r="T328" s="10"/>
     </row>
-    <row r="329" spans="1:20">
+    <row r="329" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A329" s="10"/>
       <c r="B329" s="10"/>
       <c r="C329" s="11"/>
@@ -8802,7 +8174,7 @@
       <c r="S329" s="10"/>
       <c r="T329" s="10"/>
     </row>
-    <row r="330" spans="1:20">
+    <row r="330" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A330" s="10"/>
       <c r="B330" s="10"/>
       <c r="C330" s="11"/>
@@ -8824,7 +8196,7 @@
       <c r="S330" s="10"/>
       <c r="T330" s="10"/>
     </row>
-    <row r="331" spans="1:20">
+    <row r="331" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A331" s="10"/>
       <c r="B331" s="10"/>
       <c r="C331" s="11"/>
@@ -8846,7 +8218,7 @@
       <c r="S331" s="10"/>
       <c r="T331" s="10"/>
     </row>
-    <row r="332" spans="1:20">
+    <row r="332" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A332" s="10"/>
       <c r="B332" s="10"/>
       <c r="C332" s="11"/>
@@ -8868,7 +8240,7 @@
       <c r="S332" s="10"/>
       <c r="T332" s="10"/>
     </row>
-    <row r="333" spans="1:20">
+    <row r="333" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A333" s="10"/>
       <c r="B333" s="10"/>
       <c r="C333" s="11"/>
@@ -8890,7 +8262,7 @@
       <c r="S333" s="10"/>
       <c r="T333" s="10"/>
     </row>
-    <row r="334" spans="1:20">
+    <row r="334" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A334" s="10"/>
       <c r="B334" s="10"/>
       <c r="C334" s="11"/>
@@ -8912,7 +8284,7 @@
       <c r="S334" s="10"/>
       <c r="T334" s="10"/>
     </row>
-    <row r="335" spans="1:20">
+    <row r="335" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A335" s="10"/>
       <c r="B335" s="10"/>
       <c r="C335" s="11"/>
@@ -8934,7 +8306,7 @@
       <c r="S335" s="10"/>
       <c r="T335" s="10"/>
     </row>
-    <row r="336" spans="1:20">
+    <row r="336" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A336" s="10"/>
       <c r="B336" s="10"/>
       <c r="C336" s="11"/>
@@ -8956,7 +8328,7 @@
       <c r="S336" s="10"/>
       <c r="T336" s="10"/>
     </row>
-    <row r="337" spans="1:20">
+    <row r="337" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A337" s="10"/>
       <c r="B337" s="10"/>
       <c r="C337" s="11"/>
@@ -8978,7 +8350,7 @@
       <c r="S337" s="10"/>
       <c r="T337" s="10"/>
     </row>
-    <row r="338" spans="1:20">
+    <row r="338" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A338" s="10"/>
       <c r="B338" s="10"/>
       <c r="C338" s="11"/>
@@ -9000,7 +8372,7 @@
       <c r="S338" s="10"/>
       <c r="T338" s="10"/>
     </row>
-    <row r="339" spans="1:20">
+    <row r="339" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A339" s="10"/>
       <c r="B339" s="10"/>
       <c r="C339" s="11"/>
@@ -9022,7 +8394,7 @@
       <c r="S339" s="10"/>
       <c r="T339" s="10"/>
     </row>
-    <row r="340" spans="1:20">
+    <row r="340" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A340" s="10"/>
       <c r="B340" s="10"/>
       <c r="C340" s="11"/>
@@ -9044,7 +8416,7 @@
       <c r="S340" s="10"/>
       <c r="T340" s="10"/>
     </row>
-    <row r="341" spans="1:20">
+    <row r="341" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A341" s="10"/>
       <c r="B341" s="10"/>
       <c r="C341" s="11"/>
@@ -9066,7 +8438,7 @@
       <c r="S341" s="10"/>
       <c r="T341" s="10"/>
     </row>
-    <row r="342" spans="1:20">
+    <row r="342" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A342" s="10"/>
       <c r="B342" s="10"/>
       <c r="C342" s="11"/>
@@ -9088,7 +8460,7 @@
       <c r="S342" s="10"/>
       <c r="T342" s="10"/>
     </row>
-    <row r="343" spans="1:20">
+    <row r="343" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A343" s="10"/>
       <c r="B343" s="10"/>
       <c r="C343" s="11"/>
@@ -9110,7 +8482,7 @@
       <c r="S343" s="10"/>
       <c r="T343" s="10"/>
     </row>
-    <row r="344" spans="1:20">
+    <row r="344" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A344" s="10"/>
       <c r="B344" s="10"/>
       <c r="C344" s="11"/>
@@ -9132,7 +8504,7 @@
       <c r="S344" s="10"/>
       <c r="T344" s="10"/>
     </row>
-    <row r="345" spans="1:20">
+    <row r="345" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A345" s="10"/>
       <c r="B345" s="10"/>
       <c r="C345" s="11"/>
@@ -9154,7 +8526,7 @@
       <c r="S345" s="10"/>
       <c r="T345" s="10"/>
     </row>
-    <row r="346" spans="1:20">
+    <row r="346" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A346" s="10"/>
       <c r="B346" s="10"/>
       <c r="C346" s="11"/>
@@ -9176,7 +8548,7 @@
       <c r="S346" s="10"/>
       <c r="T346" s="10"/>
     </row>
-    <row r="347" spans="1:20">
+    <row r="347" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A347" s="10"/>
       <c r="B347" s="10"/>
       <c r="C347" s="11"/>
@@ -9198,7 +8570,7 @@
       <c r="S347" s="10"/>
       <c r="T347" s="10"/>
     </row>
-    <row r="348" spans="1:20">
+    <row r="348" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A348" s="10"/>
       <c r="B348" s="10"/>
       <c r="C348" s="11"/>
@@ -9220,7 +8592,7 @@
       <c r="S348" s="10"/>
       <c r="T348" s="10"/>
     </row>
-    <row r="349" spans="1:20">
+    <row r="349" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A349" s="10"/>
       <c r="B349" s="10"/>
       <c r="C349" s="11"/>
@@ -9242,7 +8614,7 @@
       <c r="S349" s="10"/>
       <c r="T349" s="10"/>
     </row>
-    <row r="350" spans="1:20">
+    <row r="350" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A350" s="10"/>
       <c r="B350" s="10"/>
       <c r="C350" s="11"/>
@@ -9264,7 +8636,7 @@
       <c r="S350" s="10"/>
       <c r="T350" s="10"/>
     </row>
-    <row r="351" spans="1:20">
+    <row r="351" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A351" s="10"/>
       <c r="B351" s="10"/>
       <c r="C351" s="11"/>
@@ -9286,7 +8658,7 @@
       <c r="S351" s="10"/>
       <c r="T351" s="10"/>
     </row>
-    <row r="352" spans="1:20">
+    <row r="352" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A352" s="10"/>
       <c r="B352" s="10"/>
       <c r="C352" s="11"/>
@@ -9308,7 +8680,7 @@
       <c r="S352" s="10"/>
       <c r="T352" s="10"/>
     </row>
-    <row r="353" spans="1:20">
+    <row r="353" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A353" s="10"/>
       <c r="B353" s="10"/>
       <c r="C353" s="11"/>
@@ -9330,7 +8702,7 @@
       <c r="S353" s="10"/>
       <c r="T353" s="10"/>
     </row>
-    <row r="354" spans="1:20">
+    <row r="354" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A354" s="10"/>
       <c r="B354" s="10"/>
       <c r="C354" s="11"/>
@@ -9352,7 +8724,7 @@
       <c r="S354" s="10"/>
       <c r="T354" s="10"/>
     </row>
-    <row r="355" spans="1:20">
+    <row r="355" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A355" s="10"/>
       <c r="B355" s="10"/>
       <c r="C355" s="11"/>
@@ -9374,7 +8746,7 @@
       <c r="S355" s="10"/>
       <c r="T355" s="10"/>
     </row>
-    <row r="356" spans="1:20">
+    <row r="356" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A356" s="10"/>
       <c r="B356" s="10"/>
       <c r="C356" s="11"/>
@@ -9396,7 +8768,7 @@
       <c r="S356" s="10"/>
       <c r="T356" s="10"/>
     </row>
-    <row r="357" spans="1:20">
+    <row r="357" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A357" s="10"/>
       <c r="B357" s="10"/>
       <c r="C357" s="11"/>
@@ -9418,7 +8790,7 @@
       <c r="S357" s="10"/>
       <c r="T357" s="10"/>
     </row>
-    <row r="358" spans="1:20">
+    <row r="358" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A358" s="10"/>
       <c r="B358" s="10"/>
       <c r="C358" s="11"/>
@@ -9440,7 +8812,7 @@
       <c r="S358" s="10"/>
       <c r="T358" s="10"/>
     </row>
-    <row r="359" spans="1:20">
+    <row r="359" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A359" s="10"/>
       <c r="B359" s="10"/>
       <c r="C359" s="11"/>
@@ -9462,7 +8834,7 @@
       <c r="S359" s="10"/>
       <c r="T359" s="10"/>
     </row>
-    <row r="360" spans="1:20">
+    <row r="360" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A360" s="10"/>
       <c r="B360" s="10"/>
       <c r="C360" s="11"/>
@@ -9484,7 +8856,7 @@
       <c r="S360" s="10"/>
       <c r="T360" s="10"/>
     </row>
-    <row r="361" spans="1:20">
+    <row r="361" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A361" s="10"/>
       <c r="B361" s="10"/>
       <c r="C361" s="11"/>
@@ -9506,7 +8878,7 @@
       <c r="S361" s="10"/>
       <c r="T361" s="10"/>
     </row>
-    <row r="362" spans="1:20">
+    <row r="362" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A362" s="10"/>
       <c r="B362" s="10"/>
       <c r="C362" s="11"/>
@@ -9528,7 +8900,7 @@
       <c r="S362" s="10"/>
       <c r="T362" s="10"/>
     </row>
-    <row r="363" spans="1:20">
+    <row r="363" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A363" s="10"/>
       <c r="B363" s="10"/>
       <c r="C363" s="11"/>
@@ -9550,7 +8922,7 @@
       <c r="S363" s="10"/>
       <c r="T363" s="10"/>
     </row>
-    <row r="364" spans="1:20">
+    <row r="364" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A364" s="10"/>
       <c r="B364" s="10"/>
       <c r="C364" s="11"/>
@@ -9572,7 +8944,7 @@
       <c r="S364" s="10"/>
       <c r="T364" s="10"/>
     </row>
-    <row r="365" spans="1:20">
+    <row r="365" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A365" s="10"/>
       <c r="B365" s="10"/>
       <c r="C365" s="11"/>
@@ -9594,7 +8966,7 @@
       <c r="S365" s="10"/>
       <c r="T365" s="10"/>
     </row>
-    <row r="366" spans="1:20">
+    <row r="366" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A366" s="10"/>
       <c r="B366" s="10"/>
       <c r="C366" s="11"/>
@@ -9616,7 +8988,7 @@
       <c r="S366" s="10"/>
       <c r="T366" s="10"/>
     </row>
-    <row r="367" spans="1:20">
+    <row r="367" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A367" s="10"/>
       <c r="B367" s="10"/>
       <c r="C367" s="11"/>
@@ -9638,7 +9010,7 @@
       <c r="S367" s="10"/>
       <c r="T367" s="10"/>
     </row>
-    <row r="368" spans="1:20">
+    <row r="368" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A368" s="10"/>
       <c r="B368" s="10"/>
       <c r="C368" s="11"/>
@@ -9660,7 +9032,7 @@
       <c r="S368" s="10"/>
       <c r="T368" s="10"/>
     </row>
-    <row r="369" spans="1:20">
+    <row r="369" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A369" s="10"/>
       <c r="B369" s="10"/>
       <c r="C369" s="11"/>
@@ -9682,7 +9054,7 @@
       <c r="S369" s="10"/>
       <c r="T369" s="10"/>
     </row>
-    <row r="370" spans="1:20">
+    <row r="370" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A370" s="10"/>
       <c r="B370" s="10"/>
       <c r="C370" s="11"/>
@@ -9704,7 +9076,7 @@
       <c r="S370" s="10"/>
       <c r="T370" s="10"/>
     </row>
-    <row r="371" spans="1:20">
+    <row r="371" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A371" s="10"/>
       <c r="B371" s="10"/>
       <c r="C371" s="11"/>
@@ -9726,7 +9098,7 @@
       <c r="S371" s="10"/>
       <c r="T371" s="10"/>
     </row>
-    <row r="372" spans="1:20">
+    <row r="372" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A372" s="10"/>
       <c r="B372" s="10"/>
       <c r="C372" s="11"/>
@@ -9748,7 +9120,7 @@
       <c r="S372" s="10"/>
       <c r="T372" s="10"/>
     </row>
-    <row r="373" spans="1:20">
+    <row r="373" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A373" s="10"/>
       <c r="B373" s="10"/>
       <c r="C373" s="11"/>
@@ -9770,7 +9142,7 @@
       <c r="S373" s="10"/>
       <c r="T373" s="10"/>
     </row>
-    <row r="374" spans="1:20">
+    <row r="374" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A374" s="10"/>
       <c r="B374" s="10"/>
       <c r="C374" s="11"/>
@@ -9792,7 +9164,7 @@
       <c r="S374" s="10"/>
       <c r="T374" s="10"/>
     </row>
-    <row r="375" spans="1:20">
+    <row r="375" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A375" s="10"/>
       <c r="B375" s="10"/>
       <c r="C375" s="11"/>
@@ -9814,7 +9186,7 @@
       <c r="S375" s="10"/>
       <c r="T375" s="10"/>
     </row>
-    <row r="376" spans="1:20">
+    <row r="376" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A376" s="10"/>
       <c r="B376" s="10"/>
       <c r="C376" s="11"/>
@@ -9836,7 +9208,7 @@
       <c r="S376" s="10"/>
       <c r="T376" s="10"/>
     </row>
-    <row r="377" spans="1:20">
+    <row r="377" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A377" s="10"/>
       <c r="B377" s="10"/>
       <c r="C377" s="11"/>
@@ -9858,7 +9230,7 @@
       <c r="S377" s="10"/>
       <c r="T377" s="10"/>
     </row>
-    <row r="378" spans="1:20">
+    <row r="378" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A378" s="10"/>
       <c r="B378" s="10"/>
       <c r="C378" s="11"/>
@@ -9880,7 +9252,7 @@
       <c r="S378" s="10"/>
       <c r="T378" s="10"/>
     </row>
-    <row r="379" spans="1:20">
+    <row r="379" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A379" s="10"/>
       <c r="B379" s="10"/>
       <c r="C379" s="11"/>
@@ -9902,7 +9274,7 @@
       <c r="S379" s="10"/>
       <c r="T379" s="10"/>
     </row>
-    <row r="380" spans="1:20">
+    <row r="380" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A380" s="10"/>
       <c r="B380" s="10"/>
       <c r="C380" s="11"/>
@@ -9924,7 +9296,7 @@
       <c r="S380" s="10"/>
       <c r="T380" s="10"/>
     </row>
-    <row r="381" spans="1:20">
+    <row r="381" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A381" s="10"/>
       <c r="B381" s="10"/>
       <c r="C381" s="11"/>
@@ -9946,7 +9318,7 @@
       <c r="S381" s="10"/>
       <c r="T381" s="10"/>
     </row>
-    <row r="382" spans="1:20">
+    <row r="382" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A382" s="10"/>
       <c r="B382" s="10"/>
       <c r="C382" s="11"/>
@@ -9968,7 +9340,7 @@
       <c r="S382" s="10"/>
       <c r="T382" s="10"/>
     </row>
-    <row r="383" spans="1:20">
+    <row r="383" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A383" s="10"/>
       <c r="B383" s="10"/>
       <c r="C383" s="11"/>
@@ -9990,7 +9362,7 @@
       <c r="S383" s="10"/>
       <c r="T383" s="10"/>
     </row>
-    <row r="384" spans="1:20">
+    <row r="384" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A384" s="10"/>
       <c r="B384" s="10"/>
       <c r="C384" s="11"/>
@@ -10012,7 +9384,7 @@
       <c r="S384" s="10"/>
       <c r="T384" s="10"/>
     </row>
-    <row r="385" spans="1:20">
+    <row r="385" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A385" s="10"/>
       <c r="B385" s="10"/>
       <c r="C385" s="11"/>
@@ -10034,7 +9406,7 @@
       <c r="S385" s="10"/>
       <c r="T385" s="10"/>
     </row>
-    <row r="386" spans="1:20">
+    <row r="386" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A386" s="10"/>
       <c r="B386" s="10"/>
       <c r="C386" s="11"/>
@@ -10056,7 +9428,7 @@
       <c r="S386" s="10"/>
       <c r="T386" s="10"/>
     </row>
-    <row r="387" spans="1:20">
+    <row r="387" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A387" s="10"/>
       <c r="B387" s="10"/>
       <c r="C387" s="11"/>
@@ -10078,7 +9450,7 @@
       <c r="S387" s="10"/>
       <c r="T387" s="10"/>
     </row>
-    <row r="388" spans="1:20">
+    <row r="388" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A388" s="10"/>
       <c r="B388" s="10"/>
       <c r="C388" s="11"/>
@@ -10100,7 +9472,7 @@
       <c r="S388" s="10"/>
       <c r="T388" s="10"/>
     </row>
-    <row r="389" spans="1:20">
+    <row r="389" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A389" s="10"/>
       <c r="B389" s="10"/>
       <c r="C389" s="11"/>
@@ -10122,7 +9494,7 @@
       <c r="S389" s="10"/>
       <c r="T389" s="10"/>
     </row>
-    <row r="390" spans="1:20">
+    <row r="390" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A390" s="10"/>
       <c r="B390" s="10"/>
       <c r="C390" s="11"/>
@@ -10144,7 +9516,7 @@
       <c r="S390" s="10"/>
       <c r="T390" s="10"/>
     </row>
-    <row r="391" spans="1:20">
+    <row r="391" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A391" s="10"/>
       <c r="B391" s="10"/>
       <c r="C391" s="11"/>
@@ -10166,7 +9538,7 @@
       <c r="S391" s="10"/>
       <c r="T391" s="10"/>
     </row>
-    <row r="392" spans="1:20">
+    <row r="392" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A392" s="10"/>
       <c r="B392" s="10"/>
       <c r="C392" s="11"/>
@@ -10188,7 +9560,7 @@
       <c r="S392" s="10"/>
       <c r="T392" s="10"/>
     </row>
-    <row r="393" spans="1:20">
+    <row r="393" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A393" s="10"/>
       <c r="B393" s="10"/>
       <c r="C393" s="11"/>
@@ -10210,7 +9582,7 @@
       <c r="S393" s="10"/>
       <c r="T393" s="10"/>
     </row>
-    <row r="394" spans="1:20">
+    <row r="394" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A394" s="10"/>
       <c r="B394" s="10"/>
       <c r="C394" s="11"/>
@@ -10232,7 +9604,7 @@
       <c r="S394" s="10"/>
       <c r="T394" s="10"/>
     </row>
-    <row r="395" spans="1:20">
+    <row r="395" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A395" s="10"/>
       <c r="B395" s="10"/>
       <c r="C395" s="11"/>
@@ -10254,7 +9626,7 @@
       <c r="S395" s="10"/>
       <c r="T395" s="10"/>
     </row>
-    <row r="396" spans="1:20">
+    <row r="396" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A396" s="10"/>
       <c r="B396" s="10"/>
       <c r="C396" s="11"/>
@@ -10276,7 +9648,7 @@
       <c r="S396" s="10"/>
       <c r="T396" s="10"/>
     </row>
-    <row r="397" spans="1:20">
+    <row r="397" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A397" s="10"/>
       <c r="B397" s="10"/>
       <c r="C397" s="11"/>
@@ -10298,7 +9670,7 @@
       <c r="S397" s="10"/>
       <c r="T397" s="10"/>
     </row>
-    <row r="398" spans="1:20">
+    <row r="398" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A398" s="10"/>
       <c r="B398" s="10"/>
       <c r="C398" s="11"/>
@@ -10320,7 +9692,7 @@
       <c r="S398" s="10"/>
       <c r="T398" s="10"/>
     </row>
-    <row r="399" spans="1:20">
+    <row r="399" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A399" s="10"/>
       <c r="B399" s="10"/>
       <c r="C399" s="11"/>
@@ -10342,7 +9714,7 @@
       <c r="S399" s="10"/>
       <c r="T399" s="10"/>
     </row>
-    <row r="400" spans="1:20">
+    <row r="400" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A400" s="10"/>
       <c r="B400" s="10"/>
       <c r="C400" s="11"/>
@@ -10364,7 +9736,7 @@
       <c r="S400" s="10"/>
       <c r="T400" s="10"/>
     </row>
-    <row r="401" spans="1:20">
+    <row r="401" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A401" s="10"/>
       <c r="B401" s="10"/>
       <c r="C401" s="11"/>
@@ -10386,7 +9758,7 @@
       <c r="S401" s="10"/>
       <c r="T401" s="10"/>
     </row>
-    <row r="402" spans="1:20">
+    <row r="402" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A402" s="10"/>
       <c r="B402" s="10"/>
       <c r="C402" s="11"/>
@@ -10408,7 +9780,7 @@
       <c r="S402" s="10"/>
       <c r="T402" s="10"/>
     </row>
-    <row r="403" spans="1:20">
+    <row r="403" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A403" s="10"/>
       <c r="B403" s="10"/>
       <c r="C403" s="11"/>
@@ -10430,7 +9802,7 @@
       <c r="S403" s="10"/>
       <c r="T403" s="10"/>
     </row>
-    <row r="404" spans="1:20">
+    <row r="404" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A404" s="10"/>
       <c r="B404" s="10"/>
       <c r="C404" s="11"/>
@@ -10452,7 +9824,7 @@
       <c r="S404" s="10"/>
       <c r="T404" s="10"/>
     </row>
-    <row r="405" spans="1:20">
+    <row r="405" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A405" s="10"/>
       <c r="B405" s="10"/>
       <c r="C405" s="11"/>
@@ -10474,7 +9846,7 @@
       <c r="S405" s="10"/>
       <c r="T405" s="10"/>
     </row>
-    <row r="406" spans="1:20">
+    <row r="406" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A406" s="10"/>
       <c r="B406" s="10"/>
       <c r="C406" s="11"/>
@@ -10496,7 +9868,7 @@
       <c r="S406" s="10"/>
       <c r="T406" s="10"/>
     </row>
-    <row r="407" spans="1:20">
+    <row r="407" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A407" s="10"/>
       <c r="B407" s="10"/>
       <c r="C407" s="11"/>
@@ -10518,7 +9890,7 @@
       <c r="S407" s="10"/>
       <c r="T407" s="10"/>
     </row>
-    <row r="408" spans="1:20">
+    <row r="408" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A408" s="10"/>
       <c r="B408" s="10"/>
       <c r="C408" s="11"/>
@@ -10540,7 +9912,7 @@
       <c r="S408" s="10"/>
       <c r="T408" s="10"/>
     </row>
-    <row r="409" spans="1:20">
+    <row r="409" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A409" s="10"/>
       <c r="B409" s="10"/>
       <c r="C409" s="11"/>
@@ -10562,7 +9934,7 @@
       <c r="S409" s="10"/>
       <c r="T409" s="10"/>
     </row>
-    <row r="410" spans="1:20">
+    <row r="410" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A410" s="10"/>
       <c r="B410" s="10"/>
       <c r="C410" s="11"/>
@@ -10584,7 +9956,7 @@
       <c r="S410" s="10"/>
       <c r="T410" s="10"/>
     </row>
-    <row r="411" spans="1:20">
+    <row r="411" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A411" s="10"/>
       <c r="B411" s="10"/>
       <c r="C411" s="11"/>
@@ -10606,7 +9978,7 @@
       <c r="S411" s="10"/>
       <c r="T411" s="10"/>
     </row>
-    <row r="412" spans="1:20">
+    <row r="412" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A412" s="10"/>
       <c r="B412" s="10"/>
       <c r="C412" s="11"/>
@@ -10628,7 +10000,7 @@
       <c r="S412" s="10"/>
       <c r="T412" s="10"/>
     </row>
-    <row r="413" spans="1:20">
+    <row r="413" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A413" s="10"/>
       <c r="B413" s="10"/>
       <c r="C413" s="11"/>
@@ -10650,7 +10022,7 @@
       <c r="S413" s="10"/>
       <c r="T413" s="10"/>
     </row>
-    <row r="414" spans="1:20">
+    <row r="414" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A414" s="10"/>
       <c r="B414" s="10"/>
       <c r="C414" s="11"/>
@@ -10672,7 +10044,7 @@
       <c r="S414" s="10"/>
       <c r="T414" s="10"/>
     </row>
-    <row r="415" spans="1:20">
+    <row r="415" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A415" s="10"/>
       <c r="B415" s="10"/>
       <c r="C415" s="11"/>
@@ -10694,7 +10066,7 @@
       <c r="S415" s="10"/>
       <c r="T415" s="10"/>
     </row>
-    <row r="416" spans="1:20">
+    <row r="416" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A416" s="10"/>
       <c r="B416" s="10"/>
       <c r="C416" s="11"/>
@@ -10716,7 +10088,7 @@
       <c r="S416" s="10"/>
       <c r="T416" s="10"/>
     </row>
-    <row r="417" spans="1:20">
+    <row r="417" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A417" s="10"/>
       <c r="B417" s="10"/>
       <c r="C417" s="11"/>
@@ -10738,7 +10110,7 @@
       <c r="S417" s="10"/>
       <c r="T417" s="10"/>
     </row>
-    <row r="418" spans="1:20">
+    <row r="418" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A418" s="10"/>
       <c r="B418" s="10"/>
       <c r="C418" s="11"/>
@@ -10760,7 +10132,7 @@
       <c r="S418" s="10"/>
       <c r="T418" s="10"/>
     </row>
-    <row r="419" spans="1:20">
+    <row r="419" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A419" s="10"/>
       <c r="B419" s="10"/>
       <c r="C419" s="11"/>
@@ -10782,7 +10154,7 @@
       <c r="S419" s="10"/>
       <c r="T419" s="10"/>
     </row>
-    <row r="420" spans="1:20">
+    <row r="420" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A420" s="10"/>
       <c r="B420" s="10"/>
       <c r="C420" s="11"/>
@@ -10804,7 +10176,7 @@
       <c r="S420" s="10"/>
       <c r="T420" s="10"/>
     </row>
-    <row r="421" spans="1:20">
+    <row r="421" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A421" s="10"/>
       <c r="B421" s="10"/>
       <c r="C421" s="11"/>
@@ -10826,7 +10198,7 @@
       <c r="S421" s="10"/>
       <c r="T421" s="10"/>
     </row>
-    <row r="422" spans="1:20">
+    <row r="422" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A422" s="10"/>
       <c r="B422" s="10"/>
       <c r="C422" s="11"/>
@@ -10848,7 +10220,7 @@
       <c r="S422" s="10"/>
       <c r="T422" s="10"/>
     </row>
-    <row r="423" spans="1:20">
+    <row r="423" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A423" s="10"/>
       <c r="B423" s="10"/>
       <c r="C423" s="11"/>
@@ -10870,7 +10242,7 @@
       <c r="S423" s="10"/>
       <c r="T423" s="10"/>
     </row>
-    <row r="424" spans="1:20">
+    <row r="424" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A424" s="10"/>
       <c r="B424" s="10"/>
       <c r="C424" s="11"/>
@@ -10892,7 +10264,7 @@
       <c r="S424" s="10"/>
       <c r="T424" s="10"/>
     </row>
-    <row r="425" spans="1:20">
+    <row r="425" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A425" s="10"/>
       <c r="B425" s="10"/>
       <c r="C425" s="11"/>
@@ -10914,7 +10286,7 @@
       <c r="S425" s="10"/>
       <c r="T425" s="10"/>
     </row>
-    <row r="426" spans="1:20">
+    <row r="426" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A426" s="10"/>
       <c r="B426" s="10"/>
       <c r="C426" s="11"/>
@@ -10936,7 +10308,7 @@
       <c r="S426" s="10"/>
       <c r="T426" s="10"/>
     </row>
-    <row r="427" spans="1:20">
+    <row r="427" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A427" s="10"/>
       <c r="B427" s="10"/>
       <c r="C427" s="11"/>
@@ -10958,7 +10330,7 @@
       <c r="S427" s="10"/>
       <c r="T427" s="10"/>
     </row>
-    <row r="428" spans="1:20">
+    <row r="428" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A428" s="10"/>
       <c r="B428" s="10"/>
       <c r="C428" s="11"/>
@@ -10980,7 +10352,7 @@
       <c r="S428" s="10"/>
       <c r="T428" s="10"/>
     </row>
-    <row r="429" spans="1:20">
+    <row r="429" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A429" s="10"/>
       <c r="B429" s="10"/>
       <c r="C429" s="11"/>
@@ -11002,7 +10374,7 @@
       <c r="S429" s="10"/>
       <c r="T429" s="10"/>
     </row>
-    <row r="430" spans="1:20">
+    <row r="430" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A430" s="10"/>
       <c r="B430" s="10"/>
       <c r="C430" s="11"/>
@@ -11024,7 +10396,7 @@
       <c r="S430" s="10"/>
       <c r="T430" s="10"/>
     </row>
-    <row r="431" spans="1:20">
+    <row r="431" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A431" s="10"/>
       <c r="B431" s="10"/>
       <c r="C431" s="11"/>
@@ -11046,7 +10418,7 @@
       <c r="S431" s="10"/>
       <c r="T431" s="10"/>
     </row>
-    <row r="432" spans="1:20">
+    <row r="432" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A432" s="10"/>
       <c r="B432" s="10"/>
       <c r="C432" s="11"/>
@@ -11068,7 +10440,7 @@
       <c r="S432" s="10"/>
       <c r="T432" s="10"/>
     </row>
-    <row r="433" spans="1:20">
+    <row r="433" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A433" s="10"/>
       <c r="B433" s="10"/>
       <c r="C433" s="11"/>
@@ -11090,7 +10462,7 @@
       <c r="S433" s="10"/>
       <c r="T433" s="10"/>
     </row>
-    <row r="434" spans="1:20">
+    <row r="434" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A434" s="10"/>
       <c r="B434" s="10"/>
       <c r="C434" s="11"/>
@@ -11112,7 +10484,7 @@
       <c r="S434" s="10"/>
       <c r="T434" s="10"/>
     </row>
-    <row r="435" spans="1:20">
+    <row r="435" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A435" s="10"/>
       <c r="B435" s="10"/>
       <c r="C435" s="11"/>
@@ -11134,7 +10506,7 @@
       <c r="S435" s="10"/>
       <c r="T435" s="10"/>
     </row>
-    <row r="436" spans="1:20">
+    <row r="436" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A436" s="10"/>
       <c r="B436" s="10"/>
       <c r="C436" s="11"/>
@@ -11156,7 +10528,7 @@
       <c r="S436" s="10"/>
       <c r="T436" s="10"/>
     </row>
-    <row r="437" spans="1:20">
+    <row r="437" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A437" s="10"/>
       <c r="B437" s="10"/>
       <c r="C437" s="11"/>
@@ -11178,7 +10550,7 @@
       <c r="S437" s="10"/>
       <c r="T437" s="10"/>
     </row>
-    <row r="438" spans="1:20">
+    <row r="438" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A438" s="10"/>
       <c r="B438" s="10"/>
       <c r="C438" s="11"/>
@@ -11200,7 +10572,7 @@
       <c r="S438" s="10"/>
       <c r="T438" s="10"/>
     </row>
-    <row r="439" spans="1:20">
+    <row r="439" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A439" s="10"/>
       <c r="B439" s="10"/>
       <c r="C439" s="11"/>
@@ -11222,7 +10594,7 @@
       <c r="S439" s="10"/>
       <c r="T439" s="10"/>
     </row>
-    <row r="440" spans="1:20">
+    <row r="440" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A440" s="10"/>
       <c r="B440" s="10"/>
       <c r="C440" s="11"/>
@@ -11244,7 +10616,7 @@
       <c r="S440" s="10"/>
       <c r="T440" s="10"/>
     </row>
-    <row r="441" spans="1:20">
+    <row r="441" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A441" s="10"/>
       <c r="B441" s="10"/>
       <c r="C441" s="11"/>
@@ -11266,7 +10638,7 @@
       <c r="S441" s="10"/>
       <c r="T441" s="10"/>
     </row>
-    <row r="442" spans="1:20">
+    <row r="442" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A442" s="10"/>
       <c r="B442" s="10"/>
       <c r="C442" s="11"/>
@@ -11288,7 +10660,7 @@
       <c r="S442" s="10"/>
       <c r="T442" s="10"/>
     </row>
-    <row r="443" spans="1:20">
+    <row r="443" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A443" s="10"/>
       <c r="B443" s="10"/>
       <c r="C443" s="11"/>
@@ -11310,7 +10682,7 @@
       <c r="S443" s="10"/>
       <c r="T443" s="10"/>
     </row>
-    <row r="444" spans="1:20">
+    <row r="444" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A444" s="10"/>
       <c r="B444" s="10"/>
       <c r="C444" s="11"/>
@@ -11332,7 +10704,7 @@
       <c r="S444" s="10"/>
       <c r="T444" s="10"/>
     </row>
-    <row r="445" spans="1:20">
+    <row r="445" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A445" s="10"/>
       <c r="B445" s="10"/>
       <c r="C445" s="11"/>
@@ -11354,7 +10726,7 @@
       <c r="S445" s="10"/>
       <c r="T445" s="10"/>
     </row>
-    <row r="446" spans="1:20">
+    <row r="446" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A446" s="10"/>
       <c r="B446" s="10"/>
       <c r="C446" s="11"/>
@@ -11376,7 +10748,7 @@
       <c r="S446" s="10"/>
       <c r="T446" s="10"/>
     </row>
-    <row r="447" spans="1:20">
+    <row r="447" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A447" s="10"/>
       <c r="B447" s="10"/>
       <c r="C447" s="11"/>
@@ -11398,7 +10770,7 @@
       <c r="S447" s="10"/>
       <c r="T447" s="10"/>
     </row>
-    <row r="448" spans="1:20">
+    <row r="448" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A448" s="10"/>
       <c r="B448" s="10"/>
       <c r="C448" s="11"/>
@@ -11420,7 +10792,7 @@
       <c r="S448" s="10"/>
       <c r="T448" s="10"/>
     </row>
-    <row r="449" spans="1:20">
+    <row r="449" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A449" s="10"/>
       <c r="B449" s="10"/>
       <c r="C449" s="11"/>
@@ -11442,7 +10814,7 @@
       <c r="S449" s="10"/>
       <c r="T449" s="10"/>
     </row>
-    <row r="450" spans="1:20">
+    <row r="450" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A450" s="10"/>
       <c r="B450" s="10"/>
       <c r="C450" s="11"/>
@@ -11464,7 +10836,7 @@
       <c r="S450" s="10"/>
       <c r="T450" s="10"/>
     </row>
-    <row r="451" spans="1:20">
+    <row r="451" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A451" s="10"/>
       <c r="B451" s="10"/>
       <c r="C451" s="11"/>
@@ -11486,7 +10858,7 @@
       <c r="S451" s="10"/>
       <c r="T451" s="10"/>
     </row>
-    <row r="452" spans="1:20">
+    <row r="452" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A452" s="10"/>
       <c r="B452" s="10"/>
       <c r="C452" s="11"/>
@@ -11508,7 +10880,7 @@
       <c r="S452" s="10"/>
       <c r="T452" s="10"/>
     </row>
-    <row r="453" spans="1:20">
+    <row r="453" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A453" s="10"/>
       <c r="B453" s="10"/>
       <c r="C453" s="11"/>
@@ -11530,7 +10902,7 @@
       <c r="S453" s="10"/>
       <c r="T453" s="10"/>
     </row>
-    <row r="454" spans="1:20">
+    <row r="454" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A454" s="10"/>
       <c r="B454" s="10"/>
       <c r="C454" s="11"/>
@@ -11552,7 +10924,7 @@
       <c r="S454" s="10"/>
       <c r="T454" s="10"/>
     </row>
-    <row r="455" spans="1:20">
+    <row r="455" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A455" s="10"/>
       <c r="B455" s="10"/>
       <c r="C455" s="11"/>
@@ -11574,7 +10946,7 @@
       <c r="S455" s="10"/>
       <c r="T455" s="10"/>
     </row>
-    <row r="456" spans="1:20">
+    <row r="456" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A456" s="10"/>
       <c r="B456" s="10"/>
       <c r="C456" s="11"/>
@@ -11596,7 +10968,7 @@
       <c r="S456" s="10"/>
       <c r="T456" s="10"/>
     </row>
-    <row r="457" spans="1:20">
+    <row r="457" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A457" s="10"/>
       <c r="B457" s="10"/>
       <c r="C457" s="11"/>
@@ -11618,7 +10990,7 @@
       <c r="S457" s="10"/>
       <c r="T457" s="10"/>
     </row>
-    <row r="458" spans="1:20">
+    <row r="458" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A458" s="10"/>
       <c r="B458" s="10"/>
       <c r="C458" s="11"/>
@@ -11640,7 +11012,7 @@
       <c r="S458" s="10"/>
       <c r="T458" s="10"/>
     </row>
-    <row r="459" spans="1:20">
+    <row r="459" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A459" s="10"/>
       <c r="B459" s="10"/>
       <c r="C459" s="11"/>
@@ -11662,7 +11034,7 @@
       <c r="S459" s="10"/>
       <c r="T459" s="10"/>
     </row>
-    <row r="460" spans="1:20">
+    <row r="460" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A460" s="10"/>
       <c r="B460" s="10"/>
       <c r="C460" s="11"/>
@@ -11684,7 +11056,7 @@
       <c r="S460" s="10"/>
       <c r="T460" s="10"/>
     </row>
-    <row r="461" spans="1:20">
+    <row r="461" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A461" s="10"/>
       <c r="B461" s="10"/>
       <c r="C461" s="11"/>
@@ -11706,7 +11078,7 @@
       <c r="S461" s="10"/>
       <c r="T461" s="10"/>
     </row>
-    <row r="462" spans="1:20">
+    <row r="462" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A462" s="10"/>
       <c r="B462" s="10"/>
       <c r="C462" s="11"/>
@@ -11728,7 +11100,7 @@
       <c r="S462" s="10"/>
       <c r="T462" s="10"/>
     </row>
-    <row r="463" spans="1:20">
+    <row r="463" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A463" s="10"/>
       <c r="B463" s="10"/>
       <c r="C463" s="11"/>
@@ -11750,7 +11122,7 @@
       <c r="S463" s="10"/>
       <c r="T463" s="10"/>
     </row>
-    <row r="464" spans="1:20">
+    <row r="464" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A464" s="10"/>
       <c r="B464" s="10"/>
       <c r="C464" s="11"/>
@@ -11772,7 +11144,7 @@
       <c r="S464" s="10"/>
       <c r="T464" s="10"/>
     </row>
-    <row r="465" spans="1:20">
+    <row r="465" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A465" s="10"/>
       <c r="B465" s="10"/>
       <c r="C465" s="11"/>
@@ -11794,7 +11166,7 @@
       <c r="S465" s="10"/>
       <c r="T465" s="10"/>
     </row>
-    <row r="466" spans="1:20">
+    <row r="466" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A466" s="10"/>
       <c r="B466" s="10"/>
       <c r="C466" s="11"/>
@@ -11816,7 +11188,7 @@
       <c r="S466" s="10"/>
       <c r="T466" s="10"/>
     </row>
-    <row r="467" spans="1:20">
+    <row r="467" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A467" s="10"/>
       <c r="B467" s="10"/>
       <c r="C467" s="11"/>
@@ -11838,7 +11210,7 @@
       <c r="S467" s="10"/>
       <c r="T467" s="10"/>
     </row>
-    <row r="468" spans="1:20">
+    <row r="468" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A468" s="10"/>
       <c r="B468" s="10"/>
       <c r="C468" s="11"/>
@@ -11860,7 +11232,7 @@
       <c r="S468" s="10"/>
       <c r="T468" s="10"/>
     </row>
-    <row r="469" spans="1:20">
+    <row r="469" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A469" s="10"/>
       <c r="B469" s="10"/>
       <c r="C469" s="11"/>
@@ -11882,7 +11254,7 @@
       <c r="S469" s="10"/>
       <c r="T469" s="10"/>
     </row>
-    <row r="470" spans="1:20">
+    <row r="470" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A470" s="10"/>
       <c r="B470" s="10"/>
       <c r="C470" s="11"/>
@@ -11904,7 +11276,7 @@
       <c r="S470" s="10"/>
       <c r="T470" s="10"/>
     </row>
-    <row r="471" spans="1:20">
+    <row r="471" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A471" s="10"/>
       <c r="B471" s="10"/>
       <c r="C471" s="11"/>
@@ -11926,7 +11298,7 @@
       <c r="S471" s="10"/>
       <c r="T471" s="10"/>
     </row>
-    <row r="472" spans="1:20">
+    <row r="472" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A472" s="10"/>
       <c r="B472" s="10"/>
       <c r="C472" s="11"/>
@@ -11948,7 +11320,7 @@
       <c r="S472" s="10"/>
       <c r="T472" s="10"/>
     </row>
-    <row r="473" spans="1:20">
+    <row r="473" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A473" s="10"/>
       <c r="B473" s="10"/>
       <c r="C473" s="11"/>
@@ -11970,7 +11342,7 @@
       <c r="S473" s="10"/>
       <c r="T473" s="10"/>
     </row>
-    <row r="474" spans="1:20">
+    <row r="474" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A474" s="10"/>
       <c r="B474" s="10"/>
       <c r="C474" s="11"/>
@@ -11992,7 +11364,7 @@
       <c r="S474" s="10"/>
       <c r="T474" s="10"/>
     </row>
-    <row r="475" spans="1:20">
+    <row r="475" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A475" s="10"/>
       <c r="B475" s="10"/>
       <c r="C475" s="11"/>
@@ -12014,7 +11386,7 @@
       <c r="S475" s="10"/>
       <c r="T475" s="10"/>
     </row>
-    <row r="476" spans="1:20">
+    <row r="476" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A476" s="10"/>
       <c r="B476" s="10"/>
       <c r="C476" s="11"/>
@@ -12036,7 +11408,7 @@
       <c r="S476" s="10"/>
       <c r="T476" s="10"/>
     </row>
-    <row r="477" spans="1:20">
+    <row r="477" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A477" s="10"/>
       <c r="B477" s="10"/>
       <c r="C477" s="11"/>
@@ -12058,7 +11430,7 @@
       <c r="S477" s="10"/>
       <c r="T477" s="10"/>
     </row>
-    <row r="478" spans="1:20">
+    <row r="478" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A478" s="10"/>
       <c r="B478" s="10"/>
       <c r="C478" s="11"/>
@@ -12080,7 +11452,7 @@
       <c r="S478" s="10"/>
       <c r="T478" s="10"/>
     </row>
-    <row r="479" spans="1:20">
+    <row r="479" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A479" s="10"/>
       <c r="B479" s="10"/>
       <c r="C479" s="11"/>
@@ -12102,7 +11474,7 @@
       <c r="S479" s="10"/>
       <c r="T479" s="10"/>
     </row>
-    <row r="480" spans="1:20">
+    <row r="480" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A480" s="10"/>
       <c r="B480" s="10"/>
       <c r="C480" s="11"/>
@@ -12124,7 +11496,7 @@
       <c r="S480" s="10"/>
       <c r="T480" s="10"/>
     </row>
-    <row r="481" spans="1:20">
+    <row r="481" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A481" s="10"/>
       <c r="B481" s="10"/>
       <c r="C481" s="11"/>
@@ -12146,7 +11518,7 @@
       <c r="S481" s="10"/>
       <c r="T481" s="10"/>
     </row>
-    <row r="482" spans="1:20">
+    <row r="482" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A482" s="10"/>
       <c r="B482" s="10"/>
       <c r="C482" s="11"/>
@@ -12168,7 +11540,7 @@
       <c r="S482" s="10"/>
       <c r="T482" s="10"/>
     </row>
-    <row r="483" spans="1:20">
+    <row r="483" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A483" s="10"/>
       <c r="B483" s="10"/>
       <c r="C483" s="11"/>
@@ -12190,7 +11562,7 @@
       <c r="S483" s="10"/>
       <c r="T483" s="10"/>
     </row>
-    <row r="484" spans="1:20">
+    <row r="484" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A484" s="10"/>
       <c r="B484" s="10"/>
       <c r="C484" s="11"/>
@@ -12212,7 +11584,7 @@
       <c r="S484" s="10"/>
       <c r="T484" s="10"/>
     </row>
-    <row r="485" spans="1:20">
+    <row r="485" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A485" s="10"/>
       <c r="B485" s="10"/>
       <c r="C485" s="11"/>
@@ -12234,7 +11606,7 @@
       <c r="S485" s="10"/>
       <c r="T485" s="10"/>
     </row>
-    <row r="486" spans="1:20">
+    <row r="486" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A486" s="10"/>
       <c r="B486" s="10"/>
       <c r="C486" s="11"/>
@@ -12256,7 +11628,7 @@
       <c r="S486" s="10"/>
       <c r="T486" s="10"/>
     </row>
-    <row r="487" spans="1:20">
+    <row r="487" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A487" s="10"/>
       <c r="B487" s="10"/>
       <c r="C487" s="11"/>
@@ -12278,7 +11650,7 @@
       <c r="S487" s="10"/>
       <c r="T487" s="10"/>
     </row>
-    <row r="488" spans="1:20">
+    <row r="488" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A488" s="10"/>
       <c r="B488" s="10"/>
       <c r="C488" s="11"/>
@@ -12300,7 +11672,7 @@
       <c r="S488" s="10"/>
       <c r="T488" s="10"/>
     </row>
-    <row r="489" spans="1:20">
+    <row r="489" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A489" s="10"/>
       <c r="B489" s="10"/>
       <c r="C489" s="11"/>
@@ -12322,7 +11694,7 @@
       <c r="S489" s="10"/>
       <c r="T489" s="10"/>
     </row>
-    <row r="490" spans="1:20">
+    <row r="490" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A490" s="10"/>
       <c r="B490" s="10"/>
       <c r="C490" s="11"/>
@@ -12344,7 +11716,7 @@
       <c r="S490" s="10"/>
       <c r="T490" s="10"/>
     </row>
-    <row r="491" spans="1:20">
+    <row r="491" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A491" s="10"/>
       <c r="B491" s="10"/>
       <c r="C491" s="11"/>
@@ -12366,7 +11738,7 @@
       <c r="S491" s="10"/>
       <c r="T491" s="10"/>
     </row>
-    <row r="492" spans="1:20">
+    <row r="492" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A492" s="10"/>
       <c r="B492" s="10"/>
       <c r="C492" s="11"/>
@@ -12388,7 +11760,7 @@
       <c r="S492" s="10"/>
       <c r="T492" s="10"/>
     </row>
-    <row r="493" spans="1:20">
+    <row r="493" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A493" s="10"/>
       <c r="B493" s="10"/>
       <c r="C493" s="11"/>
@@ -12410,7 +11782,7 @@
       <c r="S493" s="10"/>
       <c r="T493" s="10"/>
     </row>
-    <row r="494" spans="1:20">
+    <row r="494" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A494" s="10"/>
       <c r="B494" s="10"/>
       <c r="C494" s="11"/>
@@ -12432,7 +11804,7 @@
       <c r="S494" s="10"/>
       <c r="T494" s="10"/>
     </row>
-    <row r="495" spans="1:20">
+    <row r="495" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A495" s="10"/>
       <c r="B495" s="10"/>
       <c r="C495" s="11"/>
@@ -12454,7 +11826,7 @@
       <c r="S495" s="10"/>
       <c r="T495" s="10"/>
     </row>
-    <row r="496" spans="1:20">
+    <row r="496" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A496" s="10"/>
       <c r="B496" s="10"/>
       <c r="C496" s="11"/>
@@ -12476,7 +11848,7 @@
       <c r="S496" s="10"/>
       <c r="T496" s="10"/>
     </row>
-    <row r="497" spans="1:20">
+    <row r="497" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A497" s="10"/>
       <c r="B497" s="10"/>
       <c r="C497" s="11"/>
@@ -12498,7 +11870,7 @@
       <c r="S497" s="10"/>
       <c r="T497" s="10"/>
     </row>
-    <row r="498" spans="1:20">
+    <row r="498" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A498" s="10"/>
       <c r="B498" s="10"/>
       <c r="C498" s="11"/>
@@ -12520,7 +11892,7 @@
       <c r="S498" s="10"/>
       <c r="T498" s="10"/>
     </row>
-    <row r="499" spans="1:20">
+    <row r="499" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A499" s="10"/>
       <c r="B499" s="10"/>
       <c r="C499" s="11"/>
@@ -12542,7 +11914,7 @@
       <c r="S499" s="10"/>
       <c r="T499" s="10"/>
     </row>
-    <row r="500" spans="1:20">
+    <row r="500" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A500" s="10"/>
       <c r="B500" s="10"/>
       <c r="C500" s="11"/>
@@ -12564,7 +11936,7 @@
       <c r="S500" s="10"/>
       <c r="T500" s="10"/>
     </row>
-    <row r="501" spans="1:20">
+    <row r="501" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A501" s="10"/>
       <c r="B501" s="10"/>
       <c r="C501" s="11"/>
@@ -12586,7 +11958,7 @@
       <c r="S501" s="10"/>
       <c r="T501" s="10"/>
     </row>
-    <row r="502" spans="1:20">
+    <row r="502" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A502" s="10"/>
       <c r="B502" s="10"/>
       <c r="C502" s="11"/>
@@ -12608,7 +11980,7 @@
       <c r="S502" s="10"/>
       <c r="T502" s="10"/>
     </row>
-    <row r="503" spans="1:20">
+    <row r="503" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A503" s="10"/>
       <c r="B503" s="10"/>
       <c r="C503" s="11"/>
@@ -12630,7 +12002,7 @@
       <c r="S503" s="10"/>
       <c r="T503" s="10"/>
     </row>
-    <row r="504" spans="1:20">
+    <row r="504" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A504" s="10"/>
       <c r="B504" s="10"/>
       <c r="C504" s="11"/>
@@ -12653,62 +12025,114 @@
       <c r="T504" s="10"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:T5" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A4:T5"/>
   <mergeCells count="1">
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <dataValidations count="18">
+  <dataValidations count="36">
+    <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="TIPO_PLAN admite maximo 30 caracteres." sqref="A10:A504">
+      <formula1>30</formula1>
+    </dataValidation>
     <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="TIPO_PLAN admite maximo 30 caracteres." sqref="A5:A504">
       <formula1>30</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" errorTitle="Valor no permitido" error="Tipo de documento: CC, TI, CE, PA, RC o NI." sqref="B10:B504">
+      <formula1>"CC,TI,CE,PA,RC,NI"</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" errorTitle="Valor no permitido" error="Tipo de documento: CC, TI, CE, PA, RC o NI." sqref="B5:B504">
       <formula1>"CC,TI,CE,PA,RC,NI"</formula1>
     </dataValidation>
+    <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="DOCUMENTO admite maximo 20 caracteres." sqref="C10:C504">
+      <formula1>20</formula1>
+    </dataValidation>
     <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="DOCUMENTO admite maximo 20 caracteres." sqref="C5:C504">
+      <formula1>20</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="NOMBRE1 admite maximo 20 caracteres." sqref="D10:D504">
       <formula1>20</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="NOMBRE1 admite maximo 20 caracteres." sqref="D5:D504">
       <formula1>20</formula1>
     </dataValidation>
+    <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="NOMBRE2 admite maximo 20 caracteres." sqref="E10:E504">
+      <formula1>20</formula1>
+    </dataValidation>
     <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="NOMBRE2 admite maximo 20 caracteres." sqref="E5:E504">
+      <formula1>20</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="APELLIDO1 admite maximo 20 caracteres." sqref="F10:F504">
       <formula1>20</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="APELLIDO1 admite maximo 20 caracteres." sqref="F5:F504">
       <formula1>20</formula1>
     </dataValidation>
+    <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="APELLIDO2 admite maximo 20 caracteres." sqref="G10:G504">
+      <formula1>20</formula1>
+    </dataValidation>
     <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="APELLIDO2 admite maximo 20 caracteres." sqref="G5:G504">
       <formula1>20</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" errorTitle="Valor no permitido" error="Solo se admite M o F." sqref="I10:I504">
+      <formula1>"M,F"</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" errorTitle="Valor no permitido" error="Solo se admite M o F." sqref="I5:I504">
       <formula1>"M,F"</formula1>
     </dataValidation>
+    <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="DIRECCION admite maximo 100 caracteres." sqref="J10:J504">
+      <formula1>100</formula1>
+    </dataValidation>
     <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="DIRECCION admite maximo 100 caracteres." sqref="J5:J504">
       <formula1>100</formula1>
     </dataValidation>
+    <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="CIUDAD admite maximo 50 caracteres." sqref="K10:K504">
+      <formula1>50</formula1>
+    </dataValidation>
     <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="CIUDAD admite maximo 50 caracteres." sqref="K5:K504">
+      <formula1>50</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="DEPARTAMENTO admite maximo 50 caracteres." sqref="L10:L504">
       <formula1>50</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="DEPARTAMENTO admite maximo 50 caracteres." sqref="L5:L504">
       <formula1>50</formula1>
     </dataValidation>
+    <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="CORREO admite maximo 200 caracteres." sqref="M10:M504">
+      <formula1>200</formula1>
+    </dataValidation>
     <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="CORREO admite maximo 200 caracteres." sqref="M5:M504">
       <formula1>200</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="TELEFONO admite maximo 15 caracteres." sqref="N10:N504">
+      <formula1>15</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="TELEFONO admite maximo 15 caracteres." sqref="N5:N504">
       <formula1>15</formula1>
     </dataValidation>
+    <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="EMPRESA admite maximo 100 caracteres." sqref="P10:P504">
+      <formula1>100</formula1>
+    </dataValidation>
     <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="EMPRESA admite maximo 100 caracteres." sqref="P5:P504">
+      <formula1>100</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="EPS admite maximo 100 caracteres." sqref="Q10:Q504">
       <formula1>100</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="EPS admite maximo 100 caracteres." sqref="Q5:Q504">
       <formula1>100</formula1>
     </dataValidation>
+    <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="OTRAEPS admite maximo 100 caracteres." sqref="R10:R504">
+      <formula1>100</formula1>
+    </dataValidation>
     <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="OTRAEPS admite maximo 100 caracteres." sqref="R5:R504">
       <formula1>100</formula1>
     </dataValidation>
+    <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="PLAN_SALUD admite maximo 100 caracteres." sqref="S10:S504">
+      <formula1>100</formula1>
+    </dataValidation>
     <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="PLAN_SALUD admite maximo 100 caracteres." sqref="S5:S504">
+      <formula1>100</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="PLAN_NOMBRE admite maximo 100 caracteres." sqref="T10:T504">
       <formula1>100</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Texto demasiado largo" error="PLAN_NOMBRE admite maximo 100 caracteres." sqref="T5:T504">
@@ -12716,7 +12140,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/frontend/public/plantillas/Plantilla_Carga_PlanLiga.xlsx
+++ b/frontend/public/plantillas/Plantilla_Carga_PlanLiga.xlsx
@@ -31,7 +31,7 @@
             <rFont val="SimSun"/>
           </rPr>
           <t xml:space="preserve">VARCHAR2(30)
-OBLIGATORIO
+Opcional
 Tipo de plan (ej. PLAN FAMILIAR, PLAN INDIVIDUAL). Max 30 caracteres.</t>
         </r>
       </text>
@@ -292,32 +292,18 @@
         </r>
       </text>
     </comment>
-    <comment ref="T4" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <charset val="134"/>
-            <sz val="10"/>
-            <rFont val="SimSun"/>
-          </rPr>
-          <t xml:space="preserve">VARCHAR2(100)
-OBLIGATORIO
-Nombre comercial del plan Liga (ej. PLAN LIGA ORO). Max 100 caracteres.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>PLANTILLA DE CARGA MANUAL - INTRANET_PLANLIGA</t>
   </si>
   <si>
     <t xml:space="preserve">Diligencie una fila por afiliado a partir de la fila 6. La fila 5 es un EJEMPLO: borrela antes de entregar el archivo. Las columnas con encabezado azul oscuro son OBLIGATORIAS; las de azul claro son opcionales. Pase el cursor sobre cada encabezado para ver la indicacion del campo.
-Campos obligatorios (12): TIPO_PLAN, TIPO, DOCUMENTO, NOMBRE1, APELLIDO1, FECHA_NACIMIENTO, SEXO, CIUDAD, DEPARTAMENTO, FECHA_INGRESO, EPS, PLAN_NOMBRE.</t>
+Campos obligatorios (10): TIPO, DOCUMENTO, NOMBRE1, APELLIDO1, FECHA_NACIMIENTO, SEXO, CIUDAD, DEPARTAMENTO, FECHA_INGRESO, EPS.</t>
   </si>
   <si>
     <t>TIPO_PLAN</t>
@@ -429,6 +415,9 @@
   </si>
   <si>
     <t>PLAN LIGA</t>
+  </si>
+  <si>
+    <t>COLMEDICA</t>
   </si>
 </sst>
 </file>
@@ -925,7 +914,7 @@
       <c r="L3" s="4"/>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -982,7 +971,7 @@
       <c r="S4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="T4" s="5" t="s">
+      <c r="T4" s="6" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1043,7 +1032,7 @@
         <v>37</v>
       </c>
       <c r="T5" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
